--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://yosmusic.com/yuvmayu-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c%d7%99-%d7%91%d7%a9%d7%91%d7%99%d7%9c%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>השיר הוא בלדה רכה ואינטימית שנכתבה ומבוצעת על ידי מאיה לוי ויובל גז, .צמד יוצרות צעירות שנפגשו בלימודיהן בבית הספר למוזיקה רימון. הבלדה מבטאת כמיהה נאיבית-עדינה לאהבה, ומציירת מצב רגשי של המתנה למפגש עם אדם שעדיין לא נכנס לחיים –</v>
       </c>
       <c r="G2" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H3" t="str">
-        <v>Warner Records</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H4" t="str">
-        <v>Ellise</v>
+        <v>Warner Records</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H5" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H7" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H8" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H9" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H10" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H19" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H20" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H23" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H26" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H30" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H31" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H35" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>27:54:45</v>
+        <v>4:30</v>
       </c>
       <c r="H37" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:18</v>
+        <v>27:54:45</v>
       </c>
       <c r="H38" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H40" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H43" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2088,10 +2088,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H46" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H48" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H49" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H53" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H54" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H58" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H59" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H61" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H62" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H63" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H67" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H68" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H71" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H72" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H74" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3266,10 +3266,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H80" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H81" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H82" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H83" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H86" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H87" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H88" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H90" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H91" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3874,10 +3874,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B93" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3912,10 +3912,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3950,10 +3950,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H94" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B95" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3988,10 +3988,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H96" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4064,10 +4064,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H99" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4178,7 +4178,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H100" t="str">
         <v>georgemichael</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H101" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>American Girls</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:33</v>
+        <v>3:22</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ALGO TÚ</v>
+        <v>American Girls</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
         <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Shakira</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>New Religion</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>New Religion - Single</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:54</v>
+        <v>3:33</v>
       </c>
       <c r="H104" t="str">
-        <v>Bebe Rexha</v>
+        <v>Shakira</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L104" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Where Do We Go</v>
+        <v>New Religion</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:56</v>
+        <v>2:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Ayra Starr</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L105" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ö</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H106" t="str">
-        <v>Fcukers</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L106" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>We Don’t Get Along</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>2:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Juice WRLD</v>
+        <v>Fcukers</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L107" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>bad bitch alert</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:24</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L108" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Medicine</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Medicine - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G109" t="str">
-        <v>2:34</v>
+        <v>2:24</v>
       </c>
       <c r="H109" t="str">
-        <v>Channel Tres</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L109" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H110" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L110" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G111" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H111" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L111" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dance No More</v>
+        <v>Dog</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Torn</v>
       </c>
       <c r="G112" t="str">
-        <v>3:14</v>
+        <v>2:37</v>
       </c>
       <c r="H112" t="str">
-        <v>Harry Styles</v>
+        <v>Cobrah</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L112" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Dance No More</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Anne Hathaway</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L113" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tweak</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Tweak - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:28</v>
+        <v>3:09</v>
       </c>
       <c r="H114" t="str">
-        <v>GIRLSET</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L114" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ATTITUDE</v>
+        <v>Tweak</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:05</v>
+        <v>2:28</v>
       </c>
       <c r="H115" t="str">
-        <v>aespa</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L115" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Blame Texas</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Blame Texas - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H116" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L116" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Kerosene</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Kerosene - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>The Warning</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L117" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Kerosene</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:28</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>J Balvin</v>
+        <v>The Warning</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Save Me Tonight</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:28</v>
       </c>
       <c r="H119" t="str">
-        <v>Jennifer Lopez</v>
+        <v>J Balvin</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L119" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Universal Soldier</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>HELP(2)</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:20</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Depeche Mode</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L120" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Coming Up Roses</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G121" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H121" t="str">
-        <v>Harry Styles</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L121" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G122" t="str">
-        <v>4:43</v>
+        <v>4:08</v>
       </c>
       <c r="H122" t="str">
-        <v>Noah Cyrus</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Better</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:46</v>
+        <v>4:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Koe Wetzel</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Feel Better</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>4:02</v>
+        <v>3:46</v>
       </c>
       <c r="H124" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L124" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>San Charly</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>San Charly - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:54</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Xavi</v>
+        <v>Anitta</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L126" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Timelapse de Sol</v>
+        <v>San Charly</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JuanesTeban</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H127" t="str">
-        <v>Juanes</v>
+        <v>Xavi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L127" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>USB002 REMIXES</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G128" t="str">
-        <v>4:20</v>
+        <v>3:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Juanes</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L128" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>It’s Been Too Long</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Long Long Road</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G129" t="str">
-        <v>2:42</v>
+        <v>4:20</v>
       </c>
       <c r="H129" t="str">
-        <v>Ringo Starr</v>
+        <v>Fred again..</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L129" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Atlanta</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G130" t="str">
-        <v>3:07</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L130" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Devil You Know</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Atlanta</v>
       </c>
       <c r="G131" t="str">
-        <v>3:10</v>
+        <v>3:07</v>
       </c>
       <c r="H131" t="str">
-        <v>Maya Hawke</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L131" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G132" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L132" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>400 Cities</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Miracle Mile</v>
+        <v>Jean</v>
       </c>
       <c r="G133" t="str">
-        <v>2:17</v>
+        <v>3:04</v>
       </c>
       <c r="H133" t="str">
-        <v>Paul Russell</v>
+        <v>Yebba</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L133" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>THE BOXER</v>
+        <v>400 Cities</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>THE BOXER - Single</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G134" t="str">
-        <v>3:19</v>
+        <v>2:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Kids That Fly</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L134" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Borrowed Time</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:49</v>
+        <v>3:19</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L135" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BREEZER</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lost on You</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:30</v>
+        <v>3:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Tigers Jaw</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L136" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>War To Love</v>
+        <v>BREEZER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Tragic Magic</v>
+        <v>Lost on You</v>
       </c>
       <c r="G137" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H137" t="str">
-        <v>Matt Corby</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L137" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Incompatibles</v>
+        <v>War To Love</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G138" t="str">
-        <v>2:53</v>
+        <v>3:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Christian Nodal</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L138" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Oídos Sordos</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Metamorfosis</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H139" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L139" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Angel</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Angel - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G140" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H140" t="str">
-        <v>December 10</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L140" t="str">
-        <v>Angel - December 10</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Trust Myself</v>
+        <v>Angel</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:03</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Katelyn Tarver</v>
+        <v>December 10</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L141" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tears Ago</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tears Ago - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>3:03</v>
       </c>
       <c r="H142" t="str">
-        <v>ili</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L142" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Bleed</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>House of Cards</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:40</v>
+        <v>2:35</v>
       </c>
       <c r="H143" t="str">
-        <v>The Amity Affliction</v>
+        <v>ili</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L143" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Die for You</v>
+        <v>Bleed</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Reflections</v>
+        <v>House of Cards</v>
       </c>
       <c r="G144" t="str">
-        <v>3:27</v>
+        <v>3:40</v>
       </c>
       <c r="H144" t="str">
-        <v>From Ashes to New</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L144" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Die for You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G145" t="str">
-        <v>3:35</v>
+        <v>3:27</v>
       </c>
       <c r="H145" t="str">
-        <v>Honey Dijon</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wish</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wish - Single</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:45</v>
+        <v>3:35</v>
       </c>
       <c r="H146" t="str">
-        <v>Cash Cobain</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L146" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Clean Up Song</v>
+        <v>Wish</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:46</v>
+        <v>2:45</v>
       </c>
       <c r="H147" t="str">
-        <v>Tessa Violet</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L147" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Fantasy</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Fantasy - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H148" t="str">
-        <v>Omarion</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L148" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>why am i like this</v>
+        <v>Fantasy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>why am i like this - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:56</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>bbno$</v>
+        <v>Omarion</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L149" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>How the Fire Started</v>
+        <v>why am i like this</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:55</v>
+        <v>2:56</v>
       </c>
       <c r="H150" t="str">
-        <v>Eric Nam</v>
+        <v>bbno$</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L150" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Take Off Late</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mārara</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:23</v>
+        <v>2:55</v>
       </c>
       <c r="H151" t="str">
-        <v>15 15</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L151" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>Mārara</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>15 15</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G153" t="str">
-        <v>4:06</v>
+        <v>3:13</v>
       </c>
       <c r="H153" t="str">
-        <v>Denzel Curry</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Wonderful Thing</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G154" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H154" t="str">
-        <v>aron!</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L154" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>leaving is easy</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>leaving is easy - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>2:14</v>
       </c>
       <c r="H155" t="str">
-        <v>almost monday</v>
+        <v>aron!</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L155" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>You and Me</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>You and Me - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>almost monday</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L156" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>You and Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:39</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>Lily Meola</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Everything to Nothing</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Michael Sanzone</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L158" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>DELETED</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>DELETED - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H159" t="str">
-        <v>vaultboy</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L159" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>A Thousand Years</v>
+        <v>DELETED</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:00</v>
+        <v>3:24</v>
       </c>
       <c r="H160" t="str">
-        <v>John Michael Howell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L160" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>5:29</v>
+        <v>3:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Kaskade</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L161" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:16</v>
+        <v>5:29</v>
       </c>
       <c r="H162" t="str">
-        <v>MORGXN</v>
+        <v>Kaskade</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To Myself</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>MINDFIELDS</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G163" t="str">
-        <v>3:40</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Alicia Creti</v>
+        <v>MORGXN</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L163" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>TABOO</v>
+        <v>To Myself</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>TABOO - Single</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>3:40</v>
       </c>
       <c r="H164" t="str">
-        <v>Isaiah Falls</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L164" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>TABOO</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:52</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>Two Friends</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Be Mine</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Be Mine - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:53</v>
+        <v>2:52</v>
       </c>
       <c r="H166" t="str">
-        <v>James Hype</v>
+        <v>Two Friends</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L166" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Be Mine</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:11</v>
+        <v>1:53</v>
       </c>
       <c r="H167" t="str">
-        <v>ANOTR</v>
+        <v>James Hype</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Evil Against Me</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:11</v>
       </c>
       <c r="H168" t="str">
-        <v>Shaya Zamora</v>
+        <v>ANOTR</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L168" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Still Do</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Still Do - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:03</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Anne Wilson</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L169" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>DIE 4 ME</v>
+        <v>Still Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:37</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Taylor Hill</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L170" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Havin'</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Havin' - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:49</v>
+        <v>2:37</v>
       </c>
       <c r="H171" t="str">
-        <v>1K Phew</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L171" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Havin'</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:16</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>Carolina Ross</v>
+        <v>1K Phew</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L172" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Mi Amante</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Mi Amante - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G173" t="str">
         <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Juanchito</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L173" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Pequeña</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:00</v>
+        <v>3:16</v>
       </c>
       <c r="H174" t="str">
-        <v>Flavia Laos</v>
+        <v>Juanchito</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Need it Bad</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Need it Bad - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Ama</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L175" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Time Is A Bomb</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:24</v>
+        <v>3:07</v>
       </c>
       <c r="H176" t="str">
-        <v>Metric</v>
+        <v>Ama</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L176" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>NOISE</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>NOISE - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G177" t="str">
-        <v>2:42</v>
+        <v>4:24</v>
       </c>
       <c r="H177" t="str">
-        <v>ivri</v>
+        <v>Metric</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L177" t="str">
-        <v>NOISE - ivri</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>NOISE</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Prairie</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>2:42</v>
       </c>
       <c r="H178" t="str">
-        <v>Bike Routes</v>
+        <v>ivri</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L178" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Bird Eye View</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G179" t="str">
-        <v>4:24</v>
+        <v>4:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Hayden Everett</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L179" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:46</v>
+        <v>4:24</v>
       </c>
       <c r="H180" t="str">
-        <v>Erin Rae</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L180" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Good Friend</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Singing</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:39</v>
+        <v>3:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Gia Margaret</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L181" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Good Friend</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G182" t="str">
-        <v>2:52</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L182" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Tellme</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Tellme - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H183" t="str">
-        <v>Joon</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L183" t="str">
-        <v>Tellme - Joon</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>I Can Be Yours</v>
+        <v>Tellme</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:07</v>
+        <v>3:04</v>
       </c>
       <c r="H184" t="str">
-        <v>zzzahara</v>
+        <v>Joon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L184" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soren</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Soren - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:41</v>
+        <v>4:07</v>
       </c>
       <c r="H185" t="str">
-        <v>Orca</v>
+        <v>zzzahara</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L185" t="str">
-        <v>Soren - Orca</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Gloria</v>
+        <v>Soren</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>The Guesthouse</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Shai Maestro</v>
+        <v>Orca</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L186" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gemini Eyes</v>
+        <v>Gloria</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G187" t="str">
-        <v>4:59</v>
+        <v>3:24</v>
       </c>
       <c r="H187" t="str">
-        <v>Arima Ederra</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L187" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tough</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Tough - Single</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G188" t="str">
-        <v>3:15</v>
+        <v>4:59</v>
       </c>
       <c r="H188" t="str">
-        <v>Nia Smith</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L188" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>NO HOOK</v>
+        <v>Tough</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>NO HOOK - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>1:08</v>
+        <v>3:15</v>
       </c>
       <c r="H189" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L189" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:08</v>
+        <v>1:08</v>
       </c>
       <c r="H190" t="str">
-        <v>Rosie Bennet</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mean 2 Me</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:27</v>
+        <v>4:08</v>
       </c>
       <c r="H191" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L191" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>BIG MAMA</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>4:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Flying Lotus</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L192" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Nothings What It Seems</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Midwest Memoir</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>Tyler Nance</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L193" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>No Need For Leavin'</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G194" t="str">
-        <v>3:35</v>
+        <v>3:12</v>
       </c>
       <c r="H194" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L194" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>silence outlives the earth</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:30</v>
+        <v>3:35</v>
       </c>
       <c r="H195" t="str">
-        <v>ERRA</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L195" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Poison Icon</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Crawl</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G196" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H196" t="str">
-        <v>Temple of Void</v>
+        <v>ERRA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L196" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Into Oblivion</v>
+        <v>The Crawl</v>
       </c>
       <c r="G197" t="str">
-        <v>3:13</v>
+        <v>5:12</v>
       </c>
       <c r="H197" t="str">
-        <v>Venom</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L197" t="str">
-        <v>Lay Down Your Soul - Venom</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Lay Down Your Soul</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Lay Down Your Soul - Venom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Ghost Notes</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Slave Machine</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:27</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Nervosa</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/yuvmayu-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c%d7%99-%d7%91%d7%a9%d7%91%d7%99%d7%9c%d7%9a/</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר הוא בלדה רכה ואינטימית שנכתבה ומבוצעת על ידי מאיה לוי ויובל גז, .צמד יוצרות צעירות שנפגשו בלימודיהן בבית הספר למוזיקה רימון. הבלדה מבטאת כמיהה נאיבית-עדינה לאהבה, ומציירת מצב רגשי של המתנה למפגש עם אדם שעדיין לא נכנס לחיים –</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H4" t="str">
-        <v>Warner Records</v>
+        <v>Ellise</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H5" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H6" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H7" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H8" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H9" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H11" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H13" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H15" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H17" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H20" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H21" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H22" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H23" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H25" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H29" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H30" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H33" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H35" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:30</v>
+        <v>27:54:45</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie J</v>
+        <v>BRITs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>27:54:45</v>
+        <v>5:18</v>
       </c>
       <c r="H38" t="str">
-        <v>BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H39" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H41" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H42" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H44" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2088,10 +2088,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H46" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H47" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H50" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>4:05</v>
       </c>
       <c r="H52" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>HAUSER</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H53" t="str">
-        <v>HAUSER</v>
+        <v>Queen Official</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:59</v>
+        <v>3:55</v>
       </c>
       <c r="H54" t="str">
-        <v>Queen Official</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:55</v>
+        <v>5:12</v>
       </c>
       <c r="H55" t="str">
-        <v>Tenille Townes</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Self Esteem</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H57" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H58" t="str">
-        <v>Em Beihold</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Michael Bublé</v>
+        <v>MyKey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H60" t="str">
-        <v>MyKey</v>
+        <v>Max McNown</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Max McNown</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:34</v>
+        <v>4:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>ERNEST</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>3:22</v>
       </c>
       <c r="H64" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:22</v>
+        <v>5:49</v>
       </c>
       <c r="H65" t="str">
-        <v>BLACKPINK</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Nessa Barrett</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:20</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:18</v>
+        <v>2:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Ty Myers</v>
+        <v>kenzie</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:39</v>
+        <v>3:52</v>
       </c>
       <c r="H70" t="str">
-        <v>kenzie</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H71" t="str">
-        <v>Leanna Crawford</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:01</v>
+        <v>2:54</v>
       </c>
       <c r="H72" t="str">
-        <v>Bryan Adams</v>
+        <v>CHESCA</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H73" t="str">
-        <v>CHESCA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:03</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>Dermot Kennedy</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>earMUSIC</v>
+        <v>Y2K</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3266,10 +3266,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>2:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Y2K</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:43</v>
+        <v>6:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>6:21</v>
+        <v>2:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Bryan Ferry</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:42</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Saint Harison</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H81" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Catie Turner</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:22</v>
+        <v>3:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Roxette</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:53</v>
+        <v>2:28</v>
       </c>
       <c r="H84" t="str">
-        <v>Roxette</v>
+        <v>Marcin</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:28</v>
+        <v>2:47</v>
       </c>
       <c r="H85" t="str">
-        <v>Marcin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:47</v>
+        <v>3:40</v>
       </c>
       <c r="H86" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>Ava Max</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:49</v>
+        <v>4:49</v>
       </c>
       <c r="H88" t="str">
-        <v>Ava Max</v>
+        <v>U2</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H89" t="str">
-        <v>U2</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Taylor Swift</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Kiana Ledé</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B92" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3874,10 +3874,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:38</v>
+        <v>3:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Jessie Ware</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3912,10 +3912,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:46</v>
+        <v>3:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Madison Beer</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B94" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3950,10 +3950,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:08</v>
+        <v>5:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Sean Stemaly</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H95" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4026,10 +4026,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:39</v>
+        <v>3:40</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B97" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4064,10 +4064,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>2:27</v>
       </c>
       <c r="H98" t="str">
-        <v>Self Esteem</v>
+        <v>070 Shake</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H99" t="str">
-        <v>070 Shake</v>
+        <v>georgemichael</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4178,7 +4178,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:49</v>
+        <v>5:52</v>
       </c>
       <c r="H100" t="str">
         <v>georgemichael</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:52</v>
+        <v>3:22</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>American Girls</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>3:22</v>
+        <v>3:33</v>
       </c>
       <c r="H102" t="str">
-        <v>Foo Fighters</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>American Girls</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G103" t="str">
         <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Shakira</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L103" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ALGO TÚ</v>
+        <v>New Religion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:33</v>
+        <v>2:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Shakira</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L104" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>New Religion</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>New Religion - Single</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:54</v>
+        <v>2:56</v>
       </c>
       <c r="H105" t="str">
-        <v>Bebe Rexha</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L105" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Where Do We Go</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G106" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Ayra Starr</v>
+        <v>Fcukers</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L106" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Ö</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:51</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Fcukers</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L107" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>We Don’t Get Along</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>2:24</v>
       </c>
       <c r="H108" t="str">
-        <v>Juice WRLD</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L108" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>bad bitch alert</v>
+        <v>Medicine</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:24</v>
+        <v>2:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L109" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Medicine</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Medicine - Single</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G110" t="str">
-        <v>2:34</v>
+        <v>4:11</v>
       </c>
       <c r="H110" t="str">
-        <v>Channel Tres</v>
+        <v>TOMORA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L110" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Dog</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COME CLOSER</v>
+        <v>Torn</v>
       </c>
       <c r="G111" t="str">
-        <v>4:11</v>
+        <v>2:37</v>
       </c>
       <c r="H111" t="str">
-        <v>TOMORA</v>
+        <v>Cobrah</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L111" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dog</v>
+        <v>Dance No More</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Torn</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G112" t="str">
-        <v>2:37</v>
+        <v>3:14</v>
       </c>
       <c r="H112" t="str">
-        <v>Cobrah</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L112" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dance No More</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:14</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Harry Styles</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L113" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Tweak</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:09</v>
+        <v>2:28</v>
       </c>
       <c r="H114" t="str">
-        <v>Anne Hathaway</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L114" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tweak</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tweak - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:28</v>
+        <v>3:05</v>
       </c>
       <c r="H115" t="str">
-        <v>GIRLSET</v>
+        <v>aespa</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L115" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ATTITUDE</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L116" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blame Texas</v>
+        <v>Kerosene</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Blame Texas - Single</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>3:26</v>
       </c>
       <c r="H117" t="str">
-        <v>Cody Johnson</v>
+        <v>The Warning</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L117" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Kerosene</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Kerosene - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H118" t="str">
-        <v>The Warning</v>
+        <v>J Balvin</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L118" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:28</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>J Balvin</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Save Me Tonight</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:20</v>
       </c>
       <c r="H120" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L120" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Universal Soldier</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G121" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Depeche Mode</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L121" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Coming Up Roses</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:08</v>
+        <v>4:43</v>
       </c>
       <c r="H122" t="str">
-        <v>Harry Styles</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L122" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Feel Better</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>4:43</v>
+        <v>3:46</v>
       </c>
       <c r="H123" t="str">
-        <v>Noah Cyrus</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Feel Better</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:46</v>
+        <v>4:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Koe Wetzel</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L124" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:02</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L125" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>San Charly</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>2:54</v>
       </c>
       <c r="H126" t="str">
-        <v>Anitta</v>
+        <v>Xavi</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L126" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>San Charly</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>San Charly - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G127" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Xavi</v>
+        <v>Juanes</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L127" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Timelapse de Sol</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>JuanesTeban</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H128" t="str">
-        <v>Juanes</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L128" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>USB002 REMIXES</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G129" t="str">
-        <v>4:20</v>
+        <v>2:42</v>
       </c>
       <c r="H129" t="str">
-        <v>Fred again..</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L129" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>It’s Been Too Long</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Long Long Road</v>
+        <v>Atlanta</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>3:07</v>
       </c>
       <c r="H130" t="str">
-        <v>Ringo Starr</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L130" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Atlanta</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G131" t="str">
-        <v>3:07</v>
+        <v>3:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L131" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Devil You Know</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>3:04</v>
       </c>
       <c r="H132" t="str">
-        <v>Maya Hawke</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>400 Cities</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Jean</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G133" t="str">
-        <v>3:04</v>
+        <v>2:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Yebba</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L133" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>400 Cities</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Miracle Mile</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:17</v>
+        <v>3:19</v>
       </c>
       <c r="H134" t="str">
-        <v>Paul Russell</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L134" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>THE BOXER</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>THE BOXER - Single</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:19</v>
+        <v>3:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Kids That Fly</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L135" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Borrowed Time</v>
+        <v>BREEZER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G136" t="str">
-        <v>3:49</v>
+        <v>3:30</v>
       </c>
       <c r="H136" t="str">
-        <v>Sam Barber</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L136" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BREEZER</v>
+        <v>War To Love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Lost on You</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G137" t="str">
-        <v>3:30</v>
+        <v>3:46</v>
       </c>
       <c r="H137" t="str">
-        <v>Tigers Jaw</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L137" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>War To Love</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Tragic Magic</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:46</v>
+        <v>2:53</v>
       </c>
       <c r="H138" t="str">
-        <v>Matt Corby</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L138" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Incompatibles</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G139" t="str">
-        <v>2:53</v>
+        <v>3:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Christian Nodal</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L139" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Oídos Sordos</v>
+        <v>Angel</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Metamorfosis</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H140" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>December 10</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L140" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Angel</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Angel - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:03</v>
       </c>
       <c r="H141" t="str">
-        <v>December 10</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L141" t="str">
-        <v>Angel - December 10</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Trust Myself</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:03</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>Katelyn Tarver</v>
+        <v>ili</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L142" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Tears Ago</v>
+        <v>Bleed</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Tears Ago - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G143" t="str">
-        <v>2:35</v>
+        <v>3:40</v>
       </c>
       <c r="H143" t="str">
-        <v>ili</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L143" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bleed</v>
+        <v>Die for You</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>House of Cards</v>
+        <v>Reflections</v>
       </c>
       <c r="G144" t="str">
-        <v>3:40</v>
+        <v>3:27</v>
       </c>
       <c r="H144" t="str">
-        <v>The Amity Affliction</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L144" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Die for You</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Reflections</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:27</v>
+        <v>3:35</v>
       </c>
       <c r="H145" t="str">
-        <v>From Ashes to New</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L145" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Wish</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:35</v>
+        <v>2:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Honey Dijon</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wish</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Wish - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:45</v>
+        <v>2:46</v>
       </c>
       <c r="H147" t="str">
-        <v>Cash Cobain</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L147" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Clean Up Song</v>
+        <v>Fantasy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:46</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Tessa Violet</v>
+        <v>Omarion</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L148" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Fantasy</v>
+        <v>why am i like this</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Fantasy - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>2:56</v>
       </c>
       <c r="H149" t="str">
-        <v>Omarion</v>
+        <v>bbno$</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L149" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>why am i like this</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>why am i like this - Single</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:56</v>
+        <v>2:55</v>
       </c>
       <c r="H150" t="str">
-        <v>bbno$</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L150" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>How the Fire Started</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G151" t="str">
-        <v>2:55</v>
+        <v>3:23</v>
       </c>
       <c r="H151" t="str">
-        <v>Eric Nam</v>
+        <v>15 15</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L151" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Take Off Late</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mārara</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>3:13</v>
       </c>
       <c r="H152" t="str">
-        <v>15 15</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L152" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>With No Due Respect</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G153" t="str">
-        <v>3:13</v>
+        <v>4:06</v>
       </c>
       <c r="H153" t="str">
-        <v>Foggieraw</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L153" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:06</v>
+        <v>2:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Denzel Curry</v>
+        <v>aron!</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Wonderful Thing</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:14</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>aron!</v>
+        <v>almost monday</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L155" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>leaving is easy</v>
+        <v>You and Me</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>leaving is easy - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:33</v>
+        <v>2:46</v>
       </c>
       <c r="H156" t="str">
-        <v>almost monday</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L156" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You and Me</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You and Me - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:46</v>
+        <v>2:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L157" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>3:31</v>
       </c>
       <c r="H158" t="str">
-        <v>Lily Meola</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Everything to Nothing</v>
+        <v>DELETED</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:31</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Michael Sanzone</v>
+        <v>vaultboy</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L159" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DELETED</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>DELETED - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H160" t="str">
-        <v>vaultboy</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L160" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>A Thousand Years</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:00</v>
+        <v>5:29</v>
       </c>
       <c r="H161" t="str">
-        <v>John Michael Howell</v>
+        <v>Kaskade</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L161" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G162" t="str">
-        <v>5:29</v>
+        <v>3:16</v>
       </c>
       <c r="H162" t="str">
-        <v>Kaskade</v>
+        <v>MORGXN</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L162" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>To Myself</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>3:40</v>
       </c>
       <c r="H163" t="str">
-        <v>MORGXN</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To Myself</v>
+        <v>TABOO</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>MINDFIELDS</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:40</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Alicia Creti</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L164" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>TABOO</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>TABOO - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:45</v>
+        <v>2:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Isaiah Falls</v>
+        <v>Two Friends</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L165" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>Be Mine</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:52</v>
+        <v>1:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Two Friends</v>
+        <v>James Hype</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Be Mine</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Be Mine - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>1:53</v>
+        <v>3:11</v>
       </c>
       <c r="H167" t="str">
-        <v>James Hype</v>
+        <v>ANOTR</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L167" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:11</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>ANOTR</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Evil Against Me</v>
+        <v>Still Do</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:03</v>
       </c>
       <c r="H169" t="str">
-        <v>Shaya Zamora</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L169" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Still Do</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Still Do - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>2:37</v>
       </c>
       <c r="H170" t="str">
-        <v>Anne Wilson</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L170" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>DIE 4 ME</v>
+        <v>Havin'</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>2:49</v>
       </c>
       <c r="H171" t="str">
-        <v>Taylor Hill</v>
+        <v>1K Phew</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L171" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Havin'</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Havin' - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>1K Phew</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L172" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G173" t="str">
         <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Carolina Ross</v>
+        <v>Juanchito</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L173" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Mi Amante</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Mi Amante - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:16</v>
+        <v>2:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Juanchito</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L174" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Ay Pequeña</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:00</v>
+        <v>3:07</v>
       </c>
       <c r="H175" t="str">
-        <v>Flavia Laos</v>
+        <v>Ama</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L175" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Need it Bad</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Need it Bad - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G176" t="str">
-        <v>3:07</v>
+        <v>4:24</v>
       </c>
       <c r="H176" t="str">
-        <v>Ama</v>
+        <v>Metric</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L176" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Time Is A Bomb</v>
+        <v>NOISE</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Romanticize The Dive</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:24</v>
+        <v>2:42</v>
       </c>
       <c r="H177" t="str">
-        <v>Metric</v>
+        <v>ivri</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L177" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>NOISE</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>NOISE - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G178" t="str">
-        <v>2:42</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>ivri</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L178" t="str">
-        <v>NOISE - ivri</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Prairie</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:46</v>
+        <v>4:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Bike Routes</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L179" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bird Eye View</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:24</v>
+        <v>3:46</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L180" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>Good Friend</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>3:39</v>
       </c>
       <c r="H181" t="str">
-        <v>Erin Rae</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L181" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Good Friend</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Singing</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>2:52</v>
       </c>
       <c r="H182" t="str">
-        <v>Gia Margaret</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L182" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Tellme</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:52</v>
+        <v>3:04</v>
       </c>
       <c r="H183" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Joon</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L183" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tellme</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Tellme - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:04</v>
+        <v>4:07</v>
       </c>
       <c r="H184" t="str">
-        <v>Joon</v>
+        <v>zzzahara</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L184" t="str">
-        <v>Tellme - Joon</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>I Can Be Yours</v>
+        <v>Soren</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:07</v>
+        <v>3:41</v>
       </c>
       <c r="H185" t="str">
-        <v>zzzahara</v>
+        <v>Orca</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L185" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Soren</v>
+        <v>Gloria</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soren - Single</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Orca</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L186" t="str">
-        <v>Soren - Orca</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gloria</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Guesthouse</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G187" t="str">
-        <v>3:24</v>
+        <v>4:59</v>
       </c>
       <c r="H187" t="str">
-        <v>Shai Maestro</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L187" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Gemini Eyes</v>
+        <v>Tough</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:59</v>
+        <v>3:15</v>
       </c>
       <c r="H188" t="str">
-        <v>Arima Ederra</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L188" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Tough</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Tough - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:15</v>
+        <v>1:08</v>
       </c>
       <c r="H189" t="str">
-        <v>Nia Smith</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L189" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>NO HOOK</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>NO HOOK - Single</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>1:08</v>
+        <v>4:08</v>
       </c>
       <c r="H190" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L190" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:08</v>
+        <v>4:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Rosie Bennet</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Mean 2 Me</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G192" t="str">
-        <v>4:27</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L192" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>BIG MAMA</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>3:12</v>
       </c>
       <c r="H193" t="str">
-        <v>Flying Lotus</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L193" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Nothings What It Seems</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Midwest Memoir</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:12</v>
+        <v>3:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Tyler Nance</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L194" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>No Need For Leavin'</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G195" t="str">
-        <v>3:35</v>
+        <v>3:30</v>
       </c>
       <c r="H195" t="str">
-        <v>Kameron Marlowe</v>
+        <v>ERRA</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L195" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>silence outlives the earth</v>
+        <v>The Crawl</v>
       </c>
       <c r="G196" t="str">
-        <v>3:30</v>
+        <v>5:12</v>
       </c>
       <c r="H196" t="str">
-        <v>ERRA</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L196" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Poison Icon</v>
+        <v>Lay Down Your Soul</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Crawl</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G197" t="str">
-        <v>5:12</v>
+        <v>3:13</v>
       </c>
       <c r="H197" t="str">
-        <v>Temple of Void</v>
+        <v>Venom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
       </c>
       <c r="L197" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>Lay Down Your Soul - Venom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Ghost Notes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-08</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Into Oblivion</v>
+        <v>Slave Machine</v>
       </c>
       <c r="G198" t="str">
-        <v>3:13</v>
+        <v>4:27</v>
       </c>
       <c r="H198" t="str">
-        <v>Venom</v>
+        <v>Nervosa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
       <c r="L198" t="str">
-        <v>Lay Down Your Soul - Venom</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Ghost Notes</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Slave Machine</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:27</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Nervosa</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
-      </c>
-      <c r="L199" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
       </c>
       <c r="G2" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H3" t="str">
-        <v>Warner Records</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H4" t="str">
-        <v>Ellise</v>
+        <v>Warner Records</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H5" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H7" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H8" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H9" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H10" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H19" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H20" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H23" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H26" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H30" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H31" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H35" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>27:54:45</v>
+        <v>4:30</v>
       </c>
       <c r="H37" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:18</v>
+        <v>27:54:45</v>
       </c>
       <c r="H38" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H40" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H43" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2050,10 +2050,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2088,10 +2088,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H46" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H48" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H49" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H53" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H54" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H58" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H59" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H61" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H62" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H63" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H67" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H68" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H71" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H72" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H74" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3266,10 +3266,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H80" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H81" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H82" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H83" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H86" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H87" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H88" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B89" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3760,10 +3760,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H90" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H91" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3874,10 +3874,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B93" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3912,10 +3912,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3950,10 +3950,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H94" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B95" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3988,10 +3988,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4026,10 +4026,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H96" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4064,10 +4064,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H99" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4178,7 +4178,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H100" t="str">
         <v>georgemichael</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H101" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>American Girls</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:33</v>
+        <v>3:22</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ALGO TÚ</v>
+        <v>American Girls</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
         <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Shakira</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>New Religion</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>New Religion - Single</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:54</v>
+        <v>3:33</v>
       </c>
       <c r="H104" t="str">
-        <v>Bebe Rexha</v>
+        <v>Shakira</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L104" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Where Do We Go</v>
+        <v>New Religion</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:56</v>
+        <v>2:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Ayra Starr</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L105" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ö</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H106" t="str">
-        <v>Fcukers</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L106" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>We Don’t Get Along</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>2:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Juice WRLD</v>
+        <v>Fcukers</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L107" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>bad bitch alert</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:24</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L108" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Medicine</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Medicine - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G109" t="str">
-        <v>2:34</v>
+        <v>2:24</v>
       </c>
       <c r="H109" t="str">
-        <v>Channel Tres</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L109" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H110" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L110" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G111" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H111" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L111" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dance No More</v>
+        <v>Dog</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Torn</v>
       </c>
       <c r="G112" t="str">
-        <v>3:14</v>
+        <v>2:37</v>
       </c>
       <c r="H112" t="str">
-        <v>Harry Styles</v>
+        <v>Cobrah</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L112" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Dance No More</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Anne Hathaway</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L113" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tweak</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Tweak - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:28</v>
+        <v>3:09</v>
       </c>
       <c r="H114" t="str">
-        <v>GIRLSET</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L114" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ATTITUDE</v>
+        <v>Tweak</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:05</v>
+        <v>2:28</v>
       </c>
       <c r="H115" t="str">
-        <v>aespa</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L115" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Blame Texas</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Blame Texas - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H116" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L116" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Kerosene</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Kerosene - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>The Warning</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L117" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Kerosene</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:28</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>J Balvin</v>
+        <v>The Warning</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Save Me Tonight</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:28</v>
       </c>
       <c r="H119" t="str">
-        <v>Jennifer Lopez</v>
+        <v>J Balvin</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L119" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Universal Soldier</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>HELP(2)</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:20</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Depeche Mode</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L120" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Coming Up Roses</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G121" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H121" t="str">
-        <v>Harry Styles</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L121" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G122" t="str">
-        <v>4:43</v>
+        <v>4:08</v>
       </c>
       <c r="H122" t="str">
-        <v>Noah Cyrus</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Better</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:46</v>
+        <v>4:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Koe Wetzel</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Feel Better</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>4:02</v>
+        <v>3:46</v>
       </c>
       <c r="H124" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L124" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>San Charly</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>San Charly - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:54</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Xavi</v>
+        <v>Anitta</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L126" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Timelapse de Sol</v>
+        <v>San Charly</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JuanesTeban</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H127" t="str">
-        <v>Juanes</v>
+        <v>Xavi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L127" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>USB002 REMIXES</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G128" t="str">
-        <v>4:20</v>
+        <v>3:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Juanes</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L128" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>It’s Been Too Long</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Long Long Road</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G129" t="str">
-        <v>2:42</v>
+        <v>4:20</v>
       </c>
       <c r="H129" t="str">
-        <v>Ringo Starr</v>
+        <v>Fred again..</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L129" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Atlanta</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G130" t="str">
-        <v>3:07</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L130" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Devil You Know</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Atlanta</v>
       </c>
       <c r="G131" t="str">
-        <v>3:10</v>
+        <v>3:07</v>
       </c>
       <c r="H131" t="str">
-        <v>Maya Hawke</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L131" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G132" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L132" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>400 Cities</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Miracle Mile</v>
+        <v>Jean</v>
       </c>
       <c r="G133" t="str">
-        <v>2:17</v>
+        <v>3:04</v>
       </c>
       <c r="H133" t="str">
-        <v>Paul Russell</v>
+        <v>Yebba</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L133" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>THE BOXER</v>
+        <v>400 Cities</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>THE BOXER - Single</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G134" t="str">
-        <v>3:19</v>
+        <v>2:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Kids That Fly</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L134" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Borrowed Time</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:49</v>
+        <v>3:19</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L135" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BREEZER</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lost on You</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:30</v>
+        <v>3:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Tigers Jaw</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L136" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>War To Love</v>
+        <v>BREEZER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Tragic Magic</v>
+        <v>Lost on You</v>
       </c>
       <c r="G137" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H137" t="str">
-        <v>Matt Corby</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L137" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Incompatibles</v>
+        <v>War To Love</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G138" t="str">
-        <v>2:53</v>
+        <v>3:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Christian Nodal</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L138" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Oídos Sordos</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Metamorfosis</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H139" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L139" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Angel</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Angel - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G140" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H140" t="str">
-        <v>December 10</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L140" t="str">
-        <v>Angel - December 10</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Trust Myself</v>
+        <v>Angel</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:03</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Katelyn Tarver</v>
+        <v>December 10</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L141" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tears Ago</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tears Ago - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>3:03</v>
       </c>
       <c r="H142" t="str">
-        <v>ili</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L142" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Bleed</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>House of Cards</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:40</v>
+        <v>2:35</v>
       </c>
       <c r="H143" t="str">
-        <v>The Amity Affliction</v>
+        <v>ili</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L143" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Die for You</v>
+        <v>Bleed</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Reflections</v>
+        <v>House of Cards</v>
       </c>
       <c r="G144" t="str">
-        <v>3:27</v>
+        <v>3:40</v>
       </c>
       <c r="H144" t="str">
-        <v>From Ashes to New</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L144" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Die for You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G145" t="str">
-        <v>3:35</v>
+        <v>3:27</v>
       </c>
       <c r="H145" t="str">
-        <v>Honey Dijon</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wish</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wish - Single</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:45</v>
+        <v>3:35</v>
       </c>
       <c r="H146" t="str">
-        <v>Cash Cobain</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L146" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Clean Up Song</v>
+        <v>Wish</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:46</v>
+        <v>2:45</v>
       </c>
       <c r="H147" t="str">
-        <v>Tessa Violet</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L147" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Fantasy</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Fantasy - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H148" t="str">
-        <v>Omarion</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L148" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>why am i like this</v>
+        <v>Fantasy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>why am i like this - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:56</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>bbno$</v>
+        <v>Omarion</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L149" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>How the Fire Started</v>
+        <v>why am i like this</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:55</v>
+        <v>2:56</v>
       </c>
       <c r="H150" t="str">
-        <v>Eric Nam</v>
+        <v>bbno$</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L150" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Take Off Late</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mārara</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:23</v>
+        <v>2:55</v>
       </c>
       <c r="H151" t="str">
-        <v>15 15</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L151" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>Mārara</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>15 15</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G153" t="str">
-        <v>4:06</v>
+        <v>3:13</v>
       </c>
       <c r="H153" t="str">
-        <v>Denzel Curry</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Wonderful Thing</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G154" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H154" t="str">
-        <v>aron!</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L154" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>leaving is easy</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>leaving is easy - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>2:14</v>
       </c>
       <c r="H155" t="str">
-        <v>almost monday</v>
+        <v>aron!</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L155" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>You and Me</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>You and Me - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>almost monday</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L156" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>You and Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:39</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>Lily Meola</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Everything to Nothing</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Michael Sanzone</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L158" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>DELETED</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>DELETED - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H159" t="str">
-        <v>vaultboy</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L159" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>A Thousand Years</v>
+        <v>DELETED</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:00</v>
+        <v>3:24</v>
       </c>
       <c r="H160" t="str">
-        <v>John Michael Howell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L160" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>5:29</v>
+        <v>3:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Kaskade</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L161" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:16</v>
+        <v>5:29</v>
       </c>
       <c r="H162" t="str">
-        <v>MORGXN</v>
+        <v>Kaskade</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To Myself</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>MINDFIELDS</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G163" t="str">
-        <v>3:40</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Alicia Creti</v>
+        <v>MORGXN</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L163" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>TABOO</v>
+        <v>To Myself</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>TABOO - Single</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>3:40</v>
       </c>
       <c r="H164" t="str">
-        <v>Isaiah Falls</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L164" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>TABOO</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:52</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>Two Friends</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Be Mine</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Be Mine - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:53</v>
+        <v>2:52</v>
       </c>
       <c r="H166" t="str">
-        <v>James Hype</v>
+        <v>Two Friends</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L166" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Be Mine</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:11</v>
+        <v>1:53</v>
       </c>
       <c r="H167" t="str">
-        <v>ANOTR</v>
+        <v>James Hype</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Evil Against Me</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:11</v>
       </c>
       <c r="H168" t="str">
-        <v>Shaya Zamora</v>
+        <v>ANOTR</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L168" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Still Do</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Still Do - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:03</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Anne Wilson</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L169" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>DIE 4 ME</v>
+        <v>Still Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:37</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Taylor Hill</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L170" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Havin'</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Havin' - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:49</v>
+        <v>2:37</v>
       </c>
       <c r="H171" t="str">
-        <v>1K Phew</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L171" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Havin'</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:16</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>Carolina Ross</v>
+        <v>1K Phew</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L172" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Mi Amante</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Mi Amante - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G173" t="str">
         <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Juanchito</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L173" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Pequeña</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:00</v>
+        <v>3:16</v>
       </c>
       <c r="H174" t="str">
-        <v>Flavia Laos</v>
+        <v>Juanchito</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Need it Bad</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Need it Bad - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Ama</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L175" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Time Is A Bomb</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:24</v>
+        <v>3:07</v>
       </c>
       <c r="H176" t="str">
-        <v>Metric</v>
+        <v>Ama</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L176" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>NOISE</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>NOISE - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G177" t="str">
-        <v>2:42</v>
+        <v>4:24</v>
       </c>
       <c r="H177" t="str">
-        <v>ivri</v>
+        <v>Metric</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L177" t="str">
-        <v>NOISE - ivri</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>NOISE</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Prairie</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>2:42</v>
       </c>
       <c r="H178" t="str">
-        <v>Bike Routes</v>
+        <v>ivri</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L178" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Bird Eye View</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G179" t="str">
-        <v>4:24</v>
+        <v>4:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Hayden Everett</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L179" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:46</v>
+        <v>4:24</v>
       </c>
       <c r="H180" t="str">
-        <v>Erin Rae</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L180" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Good Friend</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Singing</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:39</v>
+        <v>3:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Gia Margaret</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L181" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Good Friend</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G182" t="str">
-        <v>2:52</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L182" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Tellme</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Tellme - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H183" t="str">
-        <v>Joon</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L183" t="str">
-        <v>Tellme - Joon</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>I Can Be Yours</v>
+        <v>Tellme</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:07</v>
+        <v>3:04</v>
       </c>
       <c r="H184" t="str">
-        <v>zzzahara</v>
+        <v>Joon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L184" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soren</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Soren - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:41</v>
+        <v>4:07</v>
       </c>
       <c r="H185" t="str">
-        <v>Orca</v>
+        <v>zzzahara</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L185" t="str">
-        <v>Soren - Orca</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Gloria</v>
+        <v>Soren</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>The Guesthouse</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Shai Maestro</v>
+        <v>Orca</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L186" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gemini Eyes</v>
+        <v>Gloria</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G187" t="str">
-        <v>4:59</v>
+        <v>3:24</v>
       </c>
       <c r="H187" t="str">
-        <v>Arima Ederra</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L187" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tough</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Tough - Single</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G188" t="str">
-        <v>3:15</v>
+        <v>4:59</v>
       </c>
       <c r="H188" t="str">
-        <v>Nia Smith</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L188" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>NO HOOK</v>
+        <v>Tough</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>NO HOOK - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>1:08</v>
+        <v>3:15</v>
       </c>
       <c r="H189" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L189" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:08</v>
+        <v>1:08</v>
       </c>
       <c r="H190" t="str">
-        <v>Rosie Bennet</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mean 2 Me</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:27</v>
+        <v>4:08</v>
       </c>
       <c r="H191" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L191" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>BIG MAMA</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>4:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Flying Lotus</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L192" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Nothings What It Seems</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Midwest Memoir</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>Tyler Nance</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L193" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>No Need For Leavin'</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G194" t="str">
-        <v>3:35</v>
+        <v>3:12</v>
       </c>
       <c r="H194" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L194" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>silence outlives the earth</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:30</v>
+        <v>3:35</v>
       </c>
       <c r="H195" t="str">
-        <v>ERRA</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L195" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Poison Icon</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Crawl</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G196" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H196" t="str">
-        <v>Temple of Void</v>
+        <v>ERRA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L196" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Into Oblivion</v>
+        <v>The Crawl</v>
       </c>
       <c r="G197" t="str">
-        <v>3:13</v>
+        <v>5:12</v>
       </c>
       <c r="H197" t="str">
-        <v>Venom</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L197" t="str">
-        <v>Lay Down Your Soul - Venom</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Lay Down Your Soul</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Lay Down Your Soul - Venom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Ghost Notes</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Slave Machine</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:27</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Nervosa</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H4" t="str">
-        <v>Warner Records</v>
+        <v>Ellise</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H5" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H6" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H7" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H8" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H9" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H11" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H13" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H15" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H17" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H20" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H21" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H22" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H23" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H25" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H29" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H30" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H33" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H35" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:30</v>
+        <v>27:54:45</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie J</v>
+        <v>BRITs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>27:54:45</v>
+        <v>5:18</v>
       </c>
       <c r="H38" t="str">
-        <v>BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H39" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H41" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H42" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2050,10 +2050,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H44" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2088,10 +2088,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H46" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H47" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H50" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>4:05</v>
       </c>
       <c r="H52" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>HAUSER</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H53" t="str">
-        <v>HAUSER</v>
+        <v>Queen Official</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:59</v>
+        <v>3:55</v>
       </c>
       <c r="H54" t="str">
-        <v>Queen Official</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:55</v>
+        <v>5:12</v>
       </c>
       <c r="H55" t="str">
-        <v>Tenille Townes</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Self Esteem</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H57" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H58" t="str">
-        <v>Em Beihold</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Michael Bublé</v>
+        <v>MyKey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H60" t="str">
-        <v>MyKey</v>
+        <v>Max McNown</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Max McNown</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:34</v>
+        <v>4:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>ERNEST</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>3:22</v>
       </c>
       <c r="H64" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:22</v>
+        <v>5:49</v>
       </c>
       <c r="H65" t="str">
-        <v>BLACKPINK</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Nessa Barrett</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:20</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:18</v>
+        <v>2:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Ty Myers</v>
+        <v>kenzie</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:39</v>
+        <v>3:52</v>
       </c>
       <c r="H70" t="str">
-        <v>kenzie</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H71" t="str">
-        <v>Leanna Crawford</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:01</v>
+        <v>2:54</v>
       </c>
       <c r="H72" t="str">
-        <v>Bryan Adams</v>
+        <v>CHESCA</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H73" t="str">
-        <v>CHESCA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:03</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>Dermot Kennedy</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>earMUSIC</v>
+        <v>Y2K</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3266,10 +3266,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>2:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Y2K</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:43</v>
+        <v>6:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>6:21</v>
+        <v>2:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Bryan Ferry</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:42</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Saint Harison</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H81" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Catie Turner</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:22</v>
+        <v>3:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Roxette</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:53</v>
+        <v>2:28</v>
       </c>
       <c r="H84" t="str">
-        <v>Roxette</v>
+        <v>Marcin</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:28</v>
+        <v>2:47</v>
       </c>
       <c r="H85" t="str">
-        <v>Marcin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:47</v>
+        <v>3:40</v>
       </c>
       <c r="H86" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>Ava Max</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:49</v>
+        <v>4:49</v>
       </c>
       <c r="H88" t="str">
-        <v>Ava Max</v>
+        <v>U2</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3760,10 +3760,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H89" t="str">
-        <v>U2</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Taylor Swift</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Kiana Ledé</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B92" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3874,10 +3874,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:38</v>
+        <v>3:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Jessie Ware</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3912,10 +3912,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:46</v>
+        <v>3:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Madison Beer</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:08</v>
+        <v>5:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Sean Stemaly</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3988,10 +3988,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H95" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4026,10 +4026,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:39</v>
+        <v>3:40</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>2:27</v>
       </c>
       <c r="H98" t="str">
-        <v>Self Esteem</v>
+        <v>070 Shake</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H99" t="str">
-        <v>070 Shake</v>
+        <v>georgemichael</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4178,7 +4178,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:49</v>
+        <v>5:52</v>
       </c>
       <c r="H100" t="str">
         <v>georgemichael</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:52</v>
+        <v>3:22</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>American Girls</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>3:22</v>
+        <v>3:33</v>
       </c>
       <c r="H102" t="str">
-        <v>Foo Fighters</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>American Girls</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G103" t="str">
         <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Shakira</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L103" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ALGO TÚ</v>
+        <v>New Religion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:33</v>
+        <v>2:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Shakira</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L104" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>New Religion</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>New Religion - Single</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:54</v>
+        <v>2:56</v>
       </c>
       <c r="H105" t="str">
-        <v>Bebe Rexha</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L105" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Where Do We Go</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G106" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Ayra Starr</v>
+        <v>Fcukers</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L106" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Ö</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:51</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Fcukers</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L107" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>We Don’t Get Along</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>2:24</v>
       </c>
       <c r="H108" t="str">
-        <v>Juice WRLD</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L108" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>bad bitch alert</v>
+        <v>Medicine</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:24</v>
+        <v>2:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L109" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Medicine</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Medicine - Single</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G110" t="str">
-        <v>2:34</v>
+        <v>4:11</v>
       </c>
       <c r="H110" t="str">
-        <v>Channel Tres</v>
+        <v>TOMORA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L110" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Dog</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COME CLOSER</v>
+        <v>Torn</v>
       </c>
       <c r="G111" t="str">
-        <v>4:11</v>
+        <v>2:37</v>
       </c>
       <c r="H111" t="str">
-        <v>TOMORA</v>
+        <v>Cobrah</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L111" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dog</v>
+        <v>Dance No More</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Torn</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G112" t="str">
-        <v>2:37</v>
+        <v>3:14</v>
       </c>
       <c r="H112" t="str">
-        <v>Cobrah</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L112" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dance No More</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:14</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Harry Styles</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L113" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Tweak</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:09</v>
+        <v>2:28</v>
       </c>
       <c r="H114" t="str">
-        <v>Anne Hathaway</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L114" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tweak</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tweak - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:28</v>
+        <v>3:05</v>
       </c>
       <c r="H115" t="str">
-        <v>GIRLSET</v>
+        <v>aespa</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L115" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ATTITUDE</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L116" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blame Texas</v>
+        <v>Kerosene</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Blame Texas - Single</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>3:26</v>
       </c>
       <c r="H117" t="str">
-        <v>Cody Johnson</v>
+        <v>The Warning</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L117" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Kerosene</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Kerosene - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H118" t="str">
-        <v>The Warning</v>
+        <v>J Balvin</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L118" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:28</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>J Balvin</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Save Me Tonight</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:20</v>
       </c>
       <c r="H120" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L120" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Universal Soldier</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G121" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Depeche Mode</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L121" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Coming Up Roses</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:08</v>
+        <v>4:43</v>
       </c>
       <c r="H122" t="str">
-        <v>Harry Styles</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L122" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Feel Better</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>4:43</v>
+        <v>3:46</v>
       </c>
       <c r="H123" t="str">
-        <v>Noah Cyrus</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Feel Better</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:46</v>
+        <v>4:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Koe Wetzel</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L124" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:02</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L125" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>San Charly</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>2:54</v>
       </c>
       <c r="H126" t="str">
-        <v>Anitta</v>
+        <v>Xavi</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L126" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>San Charly</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>San Charly - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G127" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Xavi</v>
+        <v>Juanes</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L127" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Timelapse de Sol</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>JuanesTeban</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H128" t="str">
-        <v>Juanes</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L128" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>USB002 REMIXES</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G129" t="str">
-        <v>4:20</v>
+        <v>2:42</v>
       </c>
       <c r="H129" t="str">
-        <v>Fred again..</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L129" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>It’s Been Too Long</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Long Long Road</v>
+        <v>Atlanta</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>3:07</v>
       </c>
       <c r="H130" t="str">
-        <v>Ringo Starr</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L130" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Atlanta</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G131" t="str">
-        <v>3:07</v>
+        <v>3:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L131" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Devil You Know</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>3:04</v>
       </c>
       <c r="H132" t="str">
-        <v>Maya Hawke</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>400 Cities</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Jean</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G133" t="str">
-        <v>3:04</v>
+        <v>2:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Yebba</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L133" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>400 Cities</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Miracle Mile</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:17</v>
+        <v>3:19</v>
       </c>
       <c r="H134" t="str">
-        <v>Paul Russell</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L134" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>THE BOXER</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>THE BOXER - Single</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:19</v>
+        <v>3:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Kids That Fly</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L135" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Borrowed Time</v>
+        <v>BREEZER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G136" t="str">
-        <v>3:49</v>
+        <v>3:30</v>
       </c>
       <c r="H136" t="str">
-        <v>Sam Barber</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L136" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BREEZER</v>
+        <v>War To Love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Lost on You</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G137" t="str">
-        <v>3:30</v>
+        <v>3:46</v>
       </c>
       <c r="H137" t="str">
-        <v>Tigers Jaw</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L137" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>War To Love</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Tragic Magic</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:46</v>
+        <v>2:53</v>
       </c>
       <c r="H138" t="str">
-        <v>Matt Corby</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L138" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Incompatibles</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G139" t="str">
-        <v>2:53</v>
+        <v>3:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Christian Nodal</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L139" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Oídos Sordos</v>
+        <v>Angel</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Metamorfosis</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H140" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>December 10</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L140" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Angel</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Angel - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:03</v>
       </c>
       <c r="H141" t="str">
-        <v>December 10</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L141" t="str">
-        <v>Angel - December 10</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Trust Myself</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:03</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>Katelyn Tarver</v>
+        <v>ili</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L142" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Tears Ago</v>
+        <v>Bleed</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Tears Ago - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G143" t="str">
-        <v>2:35</v>
+        <v>3:40</v>
       </c>
       <c r="H143" t="str">
-        <v>ili</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L143" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bleed</v>
+        <v>Die for You</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>House of Cards</v>
+        <v>Reflections</v>
       </c>
       <c r="G144" t="str">
-        <v>3:40</v>
+        <v>3:27</v>
       </c>
       <c r="H144" t="str">
-        <v>The Amity Affliction</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L144" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Die for You</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Reflections</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:27</v>
+        <v>3:35</v>
       </c>
       <c r="H145" t="str">
-        <v>From Ashes to New</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L145" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Wish</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:35</v>
+        <v>2:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Honey Dijon</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wish</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Wish - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:45</v>
+        <v>2:46</v>
       </c>
       <c r="H147" t="str">
-        <v>Cash Cobain</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L147" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Clean Up Song</v>
+        <v>Fantasy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:46</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Tessa Violet</v>
+        <v>Omarion</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L148" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Fantasy</v>
+        <v>why am i like this</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Fantasy - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>2:56</v>
       </c>
       <c r="H149" t="str">
-        <v>Omarion</v>
+        <v>bbno$</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L149" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>why am i like this</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>why am i like this - Single</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:56</v>
+        <v>2:55</v>
       </c>
       <c r="H150" t="str">
-        <v>bbno$</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L150" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>How the Fire Started</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G151" t="str">
-        <v>2:55</v>
+        <v>3:23</v>
       </c>
       <c r="H151" t="str">
-        <v>Eric Nam</v>
+        <v>15 15</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L151" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Take Off Late</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mārara</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>3:13</v>
       </c>
       <c r="H152" t="str">
-        <v>15 15</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L152" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>With No Due Respect</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G153" t="str">
-        <v>3:13</v>
+        <v>4:06</v>
       </c>
       <c r="H153" t="str">
-        <v>Foggieraw</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L153" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:06</v>
+        <v>2:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Denzel Curry</v>
+        <v>aron!</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Wonderful Thing</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:14</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>aron!</v>
+        <v>almost monday</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L155" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>leaving is easy</v>
+        <v>You and Me</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>leaving is easy - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:33</v>
+        <v>2:46</v>
       </c>
       <c r="H156" t="str">
-        <v>almost monday</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L156" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You and Me</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You and Me - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:46</v>
+        <v>2:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L157" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>3:31</v>
       </c>
       <c r="H158" t="str">
-        <v>Lily Meola</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Everything to Nothing</v>
+        <v>DELETED</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:31</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Michael Sanzone</v>
+        <v>vaultboy</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L159" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DELETED</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>DELETED - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H160" t="str">
-        <v>vaultboy</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L160" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>A Thousand Years</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:00</v>
+        <v>5:29</v>
       </c>
       <c r="H161" t="str">
-        <v>John Michael Howell</v>
+        <v>Kaskade</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L161" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G162" t="str">
-        <v>5:29</v>
+        <v>3:16</v>
       </c>
       <c r="H162" t="str">
-        <v>Kaskade</v>
+        <v>MORGXN</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L162" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>To Myself</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>3:40</v>
       </c>
       <c r="H163" t="str">
-        <v>MORGXN</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To Myself</v>
+        <v>TABOO</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>MINDFIELDS</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:40</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Alicia Creti</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L164" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>TABOO</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>TABOO - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:45</v>
+        <v>2:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Isaiah Falls</v>
+        <v>Two Friends</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L165" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>Be Mine</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:52</v>
+        <v>1:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Two Friends</v>
+        <v>James Hype</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Be Mine</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Be Mine - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>1:53</v>
+        <v>3:11</v>
       </c>
       <c r="H167" t="str">
-        <v>James Hype</v>
+        <v>ANOTR</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L167" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:11</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>ANOTR</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Evil Against Me</v>
+        <v>Still Do</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:03</v>
       </c>
       <c r="H169" t="str">
-        <v>Shaya Zamora</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L169" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Still Do</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Still Do - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>2:37</v>
       </c>
       <c r="H170" t="str">
-        <v>Anne Wilson</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L170" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>DIE 4 ME</v>
+        <v>Havin'</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>2:49</v>
       </c>
       <c r="H171" t="str">
-        <v>Taylor Hill</v>
+        <v>1K Phew</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L171" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Havin'</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Havin' - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>1K Phew</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L172" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G173" t="str">
         <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Carolina Ross</v>
+        <v>Juanchito</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L173" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Mi Amante</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Mi Amante - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:16</v>
+        <v>2:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Juanchito</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L174" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Ay Pequeña</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:00</v>
+        <v>3:07</v>
       </c>
       <c r="H175" t="str">
-        <v>Flavia Laos</v>
+        <v>Ama</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L175" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Need it Bad</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Need it Bad - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G176" t="str">
-        <v>3:07</v>
+        <v>4:24</v>
       </c>
       <c r="H176" t="str">
-        <v>Ama</v>
+        <v>Metric</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L176" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Time Is A Bomb</v>
+        <v>NOISE</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Romanticize The Dive</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:24</v>
+        <v>2:42</v>
       </c>
       <c r="H177" t="str">
-        <v>Metric</v>
+        <v>ivri</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L177" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>NOISE</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>NOISE - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G178" t="str">
-        <v>2:42</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>ivri</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L178" t="str">
-        <v>NOISE - ivri</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Prairie</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:46</v>
+        <v>4:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Bike Routes</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L179" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bird Eye View</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:24</v>
+        <v>3:46</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L180" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>Good Friend</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>3:39</v>
       </c>
       <c r="H181" t="str">
-        <v>Erin Rae</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L181" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Good Friend</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Singing</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>2:52</v>
       </c>
       <c r="H182" t="str">
-        <v>Gia Margaret</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L182" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Tellme</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:52</v>
+        <v>3:04</v>
       </c>
       <c r="H183" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Joon</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L183" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tellme</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Tellme - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:04</v>
+        <v>4:07</v>
       </c>
       <c r="H184" t="str">
-        <v>Joon</v>
+        <v>zzzahara</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L184" t="str">
-        <v>Tellme - Joon</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>I Can Be Yours</v>
+        <v>Soren</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:07</v>
+        <v>3:41</v>
       </c>
       <c r="H185" t="str">
-        <v>zzzahara</v>
+        <v>Orca</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L185" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Soren</v>
+        <v>Gloria</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soren - Single</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Orca</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L186" t="str">
-        <v>Soren - Orca</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gloria</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Guesthouse</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G187" t="str">
-        <v>3:24</v>
+        <v>4:59</v>
       </c>
       <c r="H187" t="str">
-        <v>Shai Maestro</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L187" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Gemini Eyes</v>
+        <v>Tough</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:59</v>
+        <v>3:15</v>
       </c>
       <c r="H188" t="str">
-        <v>Arima Ederra</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L188" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Tough</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Tough - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:15</v>
+        <v>1:08</v>
       </c>
       <c r="H189" t="str">
-        <v>Nia Smith</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L189" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>NO HOOK</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>NO HOOK - Single</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>1:08</v>
+        <v>4:08</v>
       </c>
       <c r="H190" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L190" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:08</v>
+        <v>4:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Rosie Bennet</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Mean 2 Me</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G192" t="str">
-        <v>4:27</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L192" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>BIG MAMA</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>3:12</v>
       </c>
       <c r="H193" t="str">
-        <v>Flying Lotus</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L193" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Nothings What It Seems</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Midwest Memoir</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:12</v>
+        <v>3:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Tyler Nance</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L194" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>No Need For Leavin'</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G195" t="str">
-        <v>3:35</v>
+        <v>3:30</v>
       </c>
       <c r="H195" t="str">
-        <v>Kameron Marlowe</v>
+        <v>ERRA</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L195" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>silence outlives the earth</v>
+        <v>The Crawl</v>
       </c>
       <c r="G196" t="str">
-        <v>3:30</v>
+        <v>5:12</v>
       </c>
       <c r="H196" t="str">
-        <v>ERRA</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L196" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Poison Icon</v>
+        <v>Lay Down Your Soul</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Crawl</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G197" t="str">
-        <v>5:12</v>
+        <v>3:13</v>
       </c>
       <c r="H197" t="str">
-        <v>Temple of Void</v>
+        <v>Venom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
       </c>
       <c r="L197" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>Lay Down Your Soul - Venom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Ghost Notes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-08</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Into Oblivion</v>
+        <v>Slave Machine</v>
       </c>
       <c r="G198" t="str">
-        <v>3:13</v>
+        <v>4:27</v>
       </c>
       <c r="H198" t="str">
-        <v>Venom</v>
+        <v>Nervosa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
       <c r="L198" t="str">
-        <v>Lay Down Your Soul - Venom</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Ghost Notes</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Slave Machine</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:27</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Nervosa</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
-      </c>
-      <c r="L199" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409912&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>נתנאל ששון - זה רשמי</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409911&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Warner Records</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>נתנאל ששון - זה רשמי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>נתנאל אבקסיס - אין שום יאוש</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409910&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>2:33</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Ellise</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>נתנאל אבקסיס - אין שום יאוש</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409909&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>5:01</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>The Doobie Brothers</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409908&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>4:56</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>מאיר רובין - הפצע בלב</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409907&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>2:54</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Bebe Rexha</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>מאיר רובין - הפצע בלב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>טליה אלפסי - מדבר ושותק</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409906&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>2:46</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>NathanEvanss</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>טליה אלפסי - מדבר ושותק</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>חגית אסולין - שמש כבויה</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409905&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>R3HAB</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>חגית אסולין - שמש כבויה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409904&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>אבישי - מזמור לתודה</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-08</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409903&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>3:16</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>אבישי - מזמור לתודה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>3:48</v>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:29</v>
+        <v>4:58</v>
       </c>
       <c r="H13" t="str">
-        <v>Russell Dickerson</v>
+        <v>Warner Records</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:43</v>
+        <v>2:33</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Ellise</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H15" t="str">
-        <v>Matt Hansen</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:01</v>
+        <v>4:56</v>
       </c>
       <c r="H16" t="str">
-        <v>Mike Posner</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:23</v>
+        <v>2:54</v>
       </c>
       <c r="H17" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:04</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>R3HAB</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:25</v>
+        <v>3:21</v>
       </c>
       <c r="H20" t="str">
-        <v>vaultboy</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:49</v>
+        <v>3:16</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:14</v>
+        <v>2:41</v>
       </c>
       <c r="H22" t="str">
-        <v>aron!</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H23" t="str">
-        <v>Bazzi</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Sting</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:44</v>
+        <v>3:46</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:37</v>
+        <v>4:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Jessie Ware</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:52</v>
+        <v>3:23</v>
       </c>
       <c r="H27" t="str">
-        <v>Cannons</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>3:39</v>
       </c>
       <c r="H28" t="str">
-        <v>Kim Petras</v>
+        <v>almost monday</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:19</v>
+        <v>3:04</v>
       </c>
       <c r="H29" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:31</v>
+        <v>3:25</v>
       </c>
       <c r="H30" t="str">
-        <v>Kiana Ledé</v>
+        <v>vaultboy</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>3:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Ringo Starr</v>
+        <v>The Warning</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:14</v>
       </c>
       <c r="H32" t="str">
-        <v>Maya Hawke</v>
+        <v>aron!</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:55</v>
+        <v>2:43</v>
       </c>
       <c r="H33" t="str">
-        <v>Armin van Buuren</v>
+        <v>Bazzi</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:52</v>
+        <v>4:43</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Sting</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:53</v>
+        <v>2:44</v>
       </c>
       <c r="H35" t="str">
-        <v>Peter Gabriel</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:30</v>
+        <v>4:37</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>27:54:45</v>
+        <v>4:52</v>
       </c>
       <c r="H37" t="str">
-        <v>BRITs</v>
+        <v>Cannons</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:18</v>
+        <v>2:13</v>
       </c>
       <c r="H38" t="str">
-        <v>Harry Styles</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>7:20</v>
+        <v>3:19</v>
       </c>
       <c r="H39" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H40" t="str">
-        <v>BRITs</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:00</v>
+        <v>3:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:11</v>
+        <v>3:55</v>
       </c>
       <c r="H43" t="str">
-        <v>The Kiffness</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:52</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauv</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:03</v>
+        <v>2:53</v>
       </c>
       <c r="H45" t="str">
-        <v>RAYE</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:50</v>
+        <v>4:30</v>
       </c>
       <c r="H46" t="str">
-        <v>Armik</v>
+        <v>Jessie J</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:53</v>
+        <v>27:54:45</v>
       </c>
       <c r="H47" t="str">
-        <v>Scorpions</v>
+        <v>BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>5:18</v>
       </c>
       <c r="H48" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:32</v>
+        <v>7:20</v>
       </c>
       <c r="H49" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:47</v>
+        <v>3:01</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>BRITs</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>3:31</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:05</v>
+        <v>3:00</v>
       </c>
       <c r="H52" t="str">
-        <v>HAUSER</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H53" t="str">
-        <v>Queen Official</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H54" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauv</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:12</v>
+        <v>5:03</v>
       </c>
       <c r="H55" t="str">
-        <v>Self Esteem</v>
+        <v>RAYE</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>4:50</v>
       </c>
       <c r="H56" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Armik</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:18</v>
+        <v>4:53</v>
       </c>
       <c r="H57" t="str">
-        <v>Em Beihold</v>
+        <v>Scorpions</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:50</v>
+        <v>3:04</v>
       </c>
       <c r="H58" t="str">
-        <v>Michael Bublé</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:24</v>
+        <v>4:32</v>
       </c>
       <c r="H59" t="str">
-        <v>MyKey</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:36</v>
+        <v>3:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Max McNown</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>3:40</v>
       </c>
       <c r="H61" t="str">
-        <v>Megan Moroney</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:03</v>
+        <v>4:05</v>
       </c>
       <c r="H62" t="str">
-        <v>ERNEST</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>2:59</v>
       </c>
       <c r="H63" t="str">
-        <v>Bruno Mars</v>
+        <v>Queen Official</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:22</v>
+        <v>3:55</v>
       </c>
       <c r="H64" t="str">
-        <v>BLACKPINK</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:49</v>
+        <v>5:12</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2889,7 +2889,7 @@
         <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Nessa Barrett</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:20</v>
+        <v>3:18</v>
       </c>
       <c r="H67" t="str">
-        <v>Towa Bird</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>3:50</v>
       </c>
       <c r="H68" t="str">
-        <v>Ty Myers</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H69" t="str">
-        <v>kenzie</v>
+        <v>MyKey</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:52</v>
+        <v>2:36</v>
       </c>
       <c r="H70" t="str">
-        <v>Leanna Crawford</v>
+        <v>Max McNown</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H71" t="str">
-        <v>Bryan Adams</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H72" t="str">
-        <v>CHESCA</v>
+        <v>ERNEST</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H73" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>3:22</v>
       </c>
       <c r="H74" t="str">
-        <v>earMUSIC</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>5:49</v>
       </c>
       <c r="H75" t="str">
-        <v>Y2K</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:43</v>
+        <v>3:47</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>6:21</v>
+        <v>2:20</v>
       </c>
       <c r="H77" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:46</v>
+        <v>4:18</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Ferry</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>2:39</v>
       </c>
       <c r="H79" t="str">
-        <v>Saint Harison</v>
+        <v>kenzie</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>3:52</v>
       </c>
       <c r="H80" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:59</v>
+        <v>4:01</v>
       </c>
       <c r="H81" t="str">
-        <v>Catie Turner</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:22</v>
+        <v>2:54</v>
       </c>
       <c r="H82" t="str">
-        <v>Lauren Sanderson</v>
+        <v>CHESCA</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:53</v>
+        <v>4:03</v>
       </c>
       <c r="H83" t="str">
-        <v>Roxette</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:28</v>
+        <v>4:50</v>
       </c>
       <c r="H84" t="str">
-        <v>Marcin</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:47</v>
+        <v>3:06</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Y2K</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:40</v>
+        <v>2:43</v>
       </c>
       <c r="H86" t="str">
-        <v>Laufey</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:49</v>
+        <v>6:21</v>
       </c>
       <c r="H87" t="str">
-        <v>Ava Max</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:49</v>
+        <v>2:46</v>
       </c>
       <c r="H88" t="str">
-        <v>U2</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H90" t="str">
-        <v>Kiana Ledé</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H91" t="str">
-        <v>Jessie Ware</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:46</v>
+        <v>2:22</v>
       </c>
       <c r="H92" t="str">
-        <v>Madison Beer</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B93" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H93" t="str">
-        <v>Sean Stemaly</v>
+        <v>Roxette</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:32</v>
+        <v>2:28</v>
       </c>
       <c r="H94" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:39</v>
+        <v>2:47</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:40</v>
       </c>
       <c r="H96" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>2:49</v>
       </c>
       <c r="H97" t="str">
-        <v>Self Esteem</v>
+        <v>Ava Max</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H98" t="str">
-        <v>070 Shake</v>
+        <v>U2</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H99" t="str">
-        <v>georgemichael</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:52</v>
+        <v>2:59</v>
       </c>
       <c r="H100" t="str">
-        <v>georgemichael</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H101" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>American Girls</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>12 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:33</v>
+        <v>3:46</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ALGO TÚ</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:33</v>
+        <v>3:08</v>
       </c>
       <c r="H103" t="str">
-        <v>Shakira</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>New Religion</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>New Religion - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:54</v>
+        <v>5:32</v>
       </c>
       <c r="H104" t="str">
-        <v>Bebe Rexha</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Where Do We Go</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:56</v>
+        <v>4:39</v>
       </c>
       <c r="H105" t="str">
-        <v>Ayra Starr</v>
+        <v>georgemichael</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ö</v>
+        <v>13 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:51</v>
+        <v>3:40</v>
       </c>
       <c r="H106" t="str">
-        <v>Fcukers</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>We Don’t Get Along</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>3:57</v>
       </c>
       <c r="H107" t="str">
-        <v>Juice WRLD</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>bad bitch alert</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H108" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>070 Shake</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Medicine</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Medicine - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:34</v>
+        <v>4:49</v>
       </c>
       <c r="H109" t="str">
-        <v>Channel Tres</v>
+        <v>georgemichael</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>COME CLOSER</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>4:11</v>
+        <v>5:52</v>
       </c>
       <c r="H110" t="str">
-        <v>TOMORA</v>
+        <v>georgemichael</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dog</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Torn</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:37</v>
+        <v>3:22</v>
       </c>
       <c r="H111" t="str">
-        <v>Cobrah</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dance No More</v>
+        <v>American Girls</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4634,7 +4634,7 @@
         <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G112" t="str">
-        <v>3:14</v>
+        <v>3:33</v>
       </c>
       <c r="H112" t="str">
         <v>Harry Styles</v>
@@ -4646,21 +4646,21 @@
         <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L112" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>3:33</v>
       </c>
       <c r="H113" t="str">
-        <v>Anne Hathaway</v>
+        <v>Shakira</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L113" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tweak</v>
+        <v>New Religion</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Tweak - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:28</v>
+        <v>2:54</v>
       </c>
       <c r="H114" t="str">
-        <v>GIRLSET</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L114" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ATTITUDE</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:05</v>
+        <v>2:56</v>
       </c>
       <c r="H115" t="str">
-        <v>aespa</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L115" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Blame Texas</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Blame Texas - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:51</v>
       </c>
       <c r="H116" t="str">
-        <v>Cody Johnson</v>
+        <v>Fcukers</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L116" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Kerosene</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Kerosene - Single</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>2:29</v>
       </c>
       <c r="H117" t="str">
-        <v>The Warning</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L117" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:28</v>
+        <v>2:24</v>
       </c>
       <c r="H118" t="str">
-        <v>J Balvin</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L118" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Save Me Tonight</v>
+        <v>Medicine</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>2:34</v>
       </c>
       <c r="H119" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L119" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Universal Soldier</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>HELP(2)</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G120" t="str">
-        <v>3:20</v>
+        <v>4:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Depeche Mode</v>
+        <v>TOMORA</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L120" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Coming Up Roses</v>
+        <v>Dog</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Torn</v>
       </c>
       <c r="G121" t="str">
-        <v>4:08</v>
+        <v>2:37</v>
       </c>
       <c r="H121" t="str">
-        <v>Harry Styles</v>
+        <v>Cobrah</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L121" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Dance No More</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G122" t="str">
-        <v>4:43</v>
+        <v>3:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Noah Cyrus</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L122" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Better</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:46</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Koe Wetzel</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Tweak</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:02</v>
+        <v>2:28</v>
       </c>
       <c r="H124" t="str">
-        <v>Stephen Sanchez</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L124" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>3:05</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>aespa</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>San Charly</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>San Charly - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:54</v>
+        <v>3:12</v>
       </c>
       <c r="H126" t="str">
-        <v>Xavi</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L126" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Timelapse de Sol</v>
+        <v>Kerosene</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JuanesTeban</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H127" t="str">
-        <v>Juanes</v>
+        <v>The Warning</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L127" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>USB002 REMIXES</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:20</v>
+        <v>3:28</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>J Balvin</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L128" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>It’s Been Too Long</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Long Long Road</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:42</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Ringo Starr</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L129" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Atlanta</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G130" t="str">
-        <v>3:07</v>
+        <v>3:20</v>
       </c>
       <c r="H130" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L130" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Devil You Know</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G131" t="str">
-        <v>3:10</v>
+        <v>4:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Maya Hawke</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L131" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:04</v>
+        <v>4:43</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L132" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>400 Cities</v>
+        <v>Feel Better</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Miracle Mile</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>2:17</v>
+        <v>3:46</v>
       </c>
       <c r="H133" t="str">
-        <v>Paul Russell</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L133" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>THE BOXER</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>THE BOXER - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G134" t="str">
-        <v>3:19</v>
+        <v>4:02</v>
       </c>
       <c r="H134" t="str">
-        <v>Kids That Fly</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L134" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Borrowed Time</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Anitta</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L135" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BREEZER</v>
+        <v>San Charly</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lost on You</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:30</v>
+        <v>2:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Tigers Jaw</v>
+        <v>Xavi</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L136" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>War To Love</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Tragic Magic</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G137" t="str">
-        <v>3:46</v>
+        <v>3:05</v>
       </c>
       <c r="H137" t="str">
-        <v>Matt Corby</v>
+        <v>Juanes</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L137" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Incompatibles</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Incompatibles - Single</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G138" t="str">
-        <v>2:53</v>
+        <v>4:20</v>
       </c>
       <c r="H138" t="str">
-        <v>Christian Nodal</v>
+        <v>Fred again..</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L138" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Oídos Sordos</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Metamorfosis</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G139" t="str">
-        <v>3:34</v>
+        <v>2:42</v>
       </c>
       <c r="H139" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L139" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Angel</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Angel - Single</v>
+        <v>Atlanta</v>
       </c>
       <c r="G140" t="str">
-        <v>2:27</v>
+        <v>3:07</v>
       </c>
       <c r="H140" t="str">
-        <v>December 10</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L140" t="str">
-        <v>Angel - December 10</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Trust Myself</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G141" t="str">
-        <v>3:03</v>
+        <v>3:10</v>
       </c>
       <c r="H141" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L141" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tears Ago</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tears Ago - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>ili</v>
+        <v>Yebba</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L142" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Bleed</v>
+        <v>400 Cities</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>House of Cards</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G143" t="str">
-        <v>3:40</v>
+        <v>2:17</v>
       </c>
       <c r="H143" t="str">
-        <v>The Amity Affliction</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L143" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Die for You</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Reflections</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H144" t="str">
-        <v>From Ashes to New</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L144" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:35</v>
+        <v>3:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Honey Dijon</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L145" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wish</v>
+        <v>BREEZER</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wish - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G146" t="str">
-        <v>2:45</v>
+        <v>3:30</v>
       </c>
       <c r="H146" t="str">
-        <v>Cash Cobain</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L146" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Clean Up Song</v>
+        <v>War To Love</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G147" t="str">
-        <v>2:46</v>
+        <v>3:46</v>
       </c>
       <c r="H147" t="str">
-        <v>Tessa Violet</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L147" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Fantasy</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Fantasy - Single</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>2:53</v>
       </c>
       <c r="H148" t="str">
-        <v>Omarion</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L148" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>why am i like this</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>why am i like this - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G149" t="str">
-        <v>2:56</v>
+        <v>3:34</v>
       </c>
       <c r="H149" t="str">
-        <v>bbno$</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L149" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>How the Fire Started</v>
+        <v>Angel</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:55</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Eric Nam</v>
+        <v>December 10</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L150" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Take Off Late</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mārara</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G151" t="str">
-        <v>3:23</v>
+        <v>3:03</v>
       </c>
       <c r="H151" t="str">
-        <v>15 15</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L151" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>2:35</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>ili</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Bleed</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>House of Cards</v>
       </c>
       <c r="G153" t="str">
-        <v>4:06</v>
+        <v>3:40</v>
       </c>
       <c r="H153" t="str">
-        <v>Denzel Curry</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L153" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Wonderful Thing</v>
+        <v>Die for You</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G154" t="str">
-        <v>2:14</v>
+        <v>3:27</v>
       </c>
       <c r="H154" t="str">
-        <v>aron!</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L154" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>leaving is easy</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>leaving is easy - Single</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:35</v>
       </c>
       <c r="H155" t="str">
-        <v>almost monday</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L155" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>You and Me</v>
+        <v>Wish</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>You and Me - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>2:45</v>
       </c>
       <c r="H156" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L156" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>2:39</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>Lily Meola</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L157" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Everything to Nothing</v>
+        <v>Fantasy</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>3:42</v>
       </c>
       <c r="H158" t="str">
-        <v>Michael Sanzone</v>
+        <v>Omarion</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L158" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>DELETED</v>
+        <v>why am i like this</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>DELETED - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>2:56</v>
       </c>
       <c r="H159" t="str">
-        <v>vaultboy</v>
+        <v>bbno$</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L159" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>A Thousand Years</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:00</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>John Michael Howell</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L160" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G161" t="str">
-        <v>5:29</v>
+        <v>3:23</v>
       </c>
       <c r="H161" t="str">
-        <v>Kaskade</v>
+        <v>15 15</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L161" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G162" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H162" t="str">
-        <v>MORGXN</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L162" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To Myself</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>MINDFIELDS</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G163" t="str">
-        <v>3:40</v>
+        <v>4:06</v>
       </c>
       <c r="H163" t="str">
-        <v>Alicia Creti</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L163" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>TABOO</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>TABOO - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>2:14</v>
       </c>
       <c r="H164" t="str">
-        <v>Isaiah Falls</v>
+        <v>aron!</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L164" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:52</v>
+        <v>3:33</v>
       </c>
       <c r="H165" t="str">
-        <v>Two Friends</v>
+        <v>almost monday</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L165" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Be Mine</v>
+        <v>You and Me</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Be Mine - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:53</v>
+        <v>2:46</v>
       </c>
       <c r="H166" t="str">
-        <v>James Hype</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L166" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:11</v>
+        <v>2:39</v>
       </c>
       <c r="H167" t="str">
-        <v>ANOTR</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L167" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Evil Against Me</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H168" t="str">
-        <v>Shaya Zamora</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L168" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Still Do</v>
+        <v>DELETED</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Still Do - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:03</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Anne Wilson</v>
+        <v>vaultboy</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L169" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>DIE 4 ME</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:37</v>
+        <v>3:00</v>
       </c>
       <c r="H170" t="str">
-        <v>Taylor Hill</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L170" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Havin'</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Havin' - Single</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:49</v>
+        <v>5:29</v>
       </c>
       <c r="H171" t="str">
-        <v>1K Phew</v>
+        <v>Kaskade</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L171" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G172" t="str">
         <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>Carolina Ross</v>
+        <v>MORGXN</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L172" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Mi Amante</v>
+        <v>To Myself</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Mi Amante - Single</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G173" t="str">
-        <v>3:16</v>
+        <v>3:40</v>
       </c>
       <c r="H173" t="str">
-        <v>Juanchito</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L173" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Pequeña</v>
+        <v>TABOO</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:00</v>
+        <v>2:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Flavia Laos</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Need it Bad</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Need it Bad - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:07</v>
+        <v>2:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Ama</v>
+        <v>Two Friends</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L175" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Time Is A Bomb</v>
+        <v>Be Mine</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:24</v>
+        <v>1:53</v>
       </c>
       <c r="H176" t="str">
-        <v>Metric</v>
+        <v>James Hype</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L176" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>NOISE</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>NOISE - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:42</v>
+        <v>3:11</v>
       </c>
       <c r="H177" t="str">
-        <v>ivri</v>
+        <v>ANOTR</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L177" t="str">
-        <v>NOISE - ivri</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Prairie</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Bike Routes</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L178" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Bird Eye View</v>
+        <v>Still Do</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:24</v>
+        <v>3:03</v>
       </c>
       <c r="H179" t="str">
-        <v>Hayden Everett</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L179" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:46</v>
+        <v>2:37</v>
       </c>
       <c r="H180" t="str">
-        <v>Erin Rae</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L180" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Good Friend</v>
+        <v>Havin'</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Singing</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:39</v>
+        <v>2:49</v>
       </c>
       <c r="H181" t="str">
-        <v>Gia Margaret</v>
+        <v>1K Phew</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L181" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G182" t="str">
-        <v>2:52</v>
+        <v>3:16</v>
       </c>
       <c r="H182" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L182" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Tellme</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Tellme - Single</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:04</v>
+        <v>3:16</v>
       </c>
       <c r="H183" t="str">
-        <v>Joon</v>
+        <v>Juanchito</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L183" t="str">
-        <v>Tellme - Joon</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>I Can Be Yours</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>4:07</v>
+        <v>2:00</v>
       </c>
       <c r="H184" t="str">
-        <v>zzzahara</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L184" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soren</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Soren - Single</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:41</v>
+        <v>3:07</v>
       </c>
       <c r="H185" t="str">
-        <v>Orca</v>
+        <v>Ama</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L185" t="str">
-        <v>Soren - Orca</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Gloria</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>The Guesthouse</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>4:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Shai Maestro</v>
+        <v>Metric</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L186" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gemini Eyes</v>
+        <v>NOISE</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:59</v>
+        <v>2:42</v>
       </c>
       <c r="H187" t="str">
-        <v>Arima Ederra</v>
+        <v>ivri</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L187" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tough</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Tough - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G188" t="str">
-        <v>3:15</v>
+        <v>4:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Nia Smith</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L188" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>NO HOOK</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>NO HOOK - Single</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>1:08</v>
+        <v>4:24</v>
       </c>
       <c r="H189" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L189" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:08</v>
+        <v>3:46</v>
       </c>
       <c r="H190" t="str">
-        <v>Rosie Bennet</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L190" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mean 2 Me</v>
+        <v>Good Friend</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G191" t="str">
-        <v>4:27</v>
+        <v>3:39</v>
       </c>
       <c r="H191" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L191" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>BIG MAMA</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>Flying Lotus</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L192" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Nothings What It Seems</v>
+        <v>Tellme</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Midwest Memoir</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>Tyler Nance</v>
+        <v>Joon</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L193" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>No Need For Leavin'</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:35</v>
+        <v>4:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Kameron Marlowe</v>
+        <v>zzzahara</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L194" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>Soren</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>silence outlives the earth</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:30</v>
+        <v>3:41</v>
       </c>
       <c r="H195" t="str">
-        <v>ERRA</v>
+        <v>Orca</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L195" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Poison Icon</v>
+        <v>Gloria</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Crawl</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G196" t="str">
-        <v>5:12</v>
+        <v>3:24</v>
       </c>
       <c r="H196" t="str">
-        <v>Temple of Void</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L196" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,68 +7861,448 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Into Oblivion</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G197" t="str">
-        <v>3:13</v>
+        <v>4:59</v>
       </c>
       <c r="H197" t="str">
-        <v>Venom</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L197" t="str">
-        <v>Lay Down Your Soul - Venom</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Tough</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Tough - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:15</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Nia Smith</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Tough - Nia Smith</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>NO HOOK</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>NO HOOK - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>1:08</v>
+      </c>
+      <c r="H199" t="str">
+        <v>KARRAHBOOO</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+      </c>
+      <c r="L199" t="str">
+        <v>NO HOOK - KARRAHBOOO</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Rosie Bennet</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+      </c>
+      <c r="L200" t="str">
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Mean 2 Me</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Mean 2 Me - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>4:27</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Skyla Tylaa</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Mean 2 Me - Skyla Tylaa</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>CAPTAIN KERNEL</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>BIG MAMA</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Flying Lotus</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+      </c>
+      <c r="L202" t="str">
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Nothings What It Seems</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Midwest Memoir</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:12</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Tyler Nance</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Nothings What It Seems - Tyler Nance</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>No Need For Leavin'</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>No Need For Leavin' - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+      </c>
+      <c r="L204" t="str">
+        <v>No Need For Leavin' - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>ii. in the gut of the wolf</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>silence outlives the earth</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:30</v>
+      </c>
+      <c r="H205" t="str">
+        <v>ERRA</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+      </c>
+      <c r="L205" t="str">
+        <v>ii. in the gut of the wolf - ERRA</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Poison Icon</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>The Crawl</v>
+      </c>
+      <c r="G206" t="str">
+        <v>5:12</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Temple of Void</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Poison Icon - Temple of Void</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Lay Down Your Soul</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Lay Down Your Soul - Venom</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
         <v>Ghost Notes</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D208" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
         <v>Slave Machine</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G208" t="str">
         <v>4:27</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H208" t="str">
         <v>Nervosa</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
         <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K208" t="str">
         <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L208" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409912&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409911&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Warner Records</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409910&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2:33</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Ellise</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409909&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>5:01</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409908&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>4:56</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409907&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2:54</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409906&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-08</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>2:46</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>NathanEvanss</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409905&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-08</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>2:56</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>R3HAB</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409904&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-08</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי - מזמור לתודה</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409903&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-08</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>3:16</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי - מזמור לתודה</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-08</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:48</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>Harry Styles</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-08</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:58</v>
+        <v>2:29</v>
       </c>
       <c r="H13" t="str">
-        <v>Warner Records</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-08</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:33</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>Ellise</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-08</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:01</v>
+        <v>3:46</v>
       </c>
       <c r="H15" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-08</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:56</v>
+        <v>4:01</v>
       </c>
       <c r="H16" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-08</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:54</v>
+        <v>3:23</v>
       </c>
       <c r="H17" t="str">
-        <v>Bebe Rexha</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-08</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:46</v>
+        <v>3:39</v>
       </c>
       <c r="H18" t="str">
-        <v>NathanEvanss</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:56</v>
+        <v>3:04</v>
       </c>
       <c r="H19" t="str">
-        <v>R3HAB</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:21</v>
+        <v>3:25</v>
       </c>
       <c r="H20" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>vaultboy</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:16</v>
+        <v>3:49</v>
       </c>
       <c r="H21" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:41</v>
+        <v>2:14</v>
       </c>
       <c r="H22" t="str">
-        <v>Johnny Orlando</v>
+        <v>aron!</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H23" t="str">
-        <v>Russell Dickerson</v>
+        <v>Bazzi</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H24" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Sting</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-08</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:46</v>
+        <v>2:44</v>
       </c>
       <c r="H25" t="str">
-        <v>Matt Hansen</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-08</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:01</v>
+        <v>4:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Mike Posner</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-08</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:23</v>
+        <v>4:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:39</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>almost monday</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:04</v>
+        <v>3:19</v>
       </c>
       <c r="H29" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:25</v>
+        <v>2:31</v>
       </c>
       <c r="H30" t="str">
-        <v>vaultboy</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:49</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>The Warning</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:14</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>aron!</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:43</v>
+        <v>3:55</v>
       </c>
       <c r="H33" t="str">
-        <v>Bazzi</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:43</v>
+        <v>3:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Sting</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:44</v>
+        <v>2:53</v>
       </c>
       <c r="H35" t="str">
-        <v>Dean Lewis</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:37</v>
+        <v>4:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie Ware</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:52</v>
+        <v>27:54:45</v>
       </c>
       <c r="H37" t="str">
-        <v>Cannons</v>
+        <v>BRITs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:13</v>
+        <v>5:18</v>
       </c>
       <c r="H38" t="str">
-        <v>Kim Petras</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:19</v>
+        <v>7:20</v>
       </c>
       <c r="H39" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:31</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>Kiana Ledé</v>
+        <v>BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H41" t="str">
-        <v>Ringo Starr</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:10</v>
+        <v>3:00</v>
       </c>
       <c r="H42" t="str">
-        <v>Maya Hawke</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:55</v>
+        <v>3:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:52</v>
+        <v>3:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Demi Lovato</v>
+        <v>Lauv</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:53</v>
+        <v>5:03</v>
       </c>
       <c r="H45" t="str">
-        <v>Peter Gabriel</v>
+        <v>RAYE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:30</v>
+        <v>4:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Jessie J</v>
+        <v>Armik</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B47" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>27:54:45</v>
+        <v>4:53</v>
       </c>
       <c r="H47" t="str">
-        <v>BRITs</v>
+        <v>Scorpions</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:18</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>7:20</v>
+        <v>4:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:01</v>
+        <v>3:47</v>
       </c>
       <c r="H50" t="str">
-        <v>BRITs</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:31</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:00</v>
+        <v>4:05</v>
       </c>
       <c r="H52" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>HAUSER</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:11</v>
+        <v>2:59</v>
       </c>
       <c r="H53" t="str">
-        <v>The Kiffness</v>
+        <v>Queen Official</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:32</v>
+        <v>3:55</v>
       </c>
       <c r="H54" t="str">
-        <v>Lauv</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:03</v>
+        <v>5:12</v>
       </c>
       <c r="H55" t="str">
-        <v>RAYE</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:50</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Armik</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H57" t="str">
-        <v>Scorpions</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:04</v>
+        <v>3:50</v>
       </c>
       <c r="H58" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:32</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>MyKey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-08</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:47</v>
+        <v>2:36</v>
       </c>
       <c r="H60" t="str">
-        <v>Girl Tones</v>
+        <v>Max McNown</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-08</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:40</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:05</v>
+        <v>4:03</v>
       </c>
       <c r="H62" t="str">
-        <v>HAUSER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:59</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Queen Official</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:55</v>
+        <v>3:22</v>
       </c>
       <c r="H64" t="str">
-        <v>Tenille Townes</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:12</v>
+        <v>5:49</v>
       </c>
       <c r="H65" t="str">
-        <v>Self Esteem</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-08</v>
@@ -2889,7 +2889,7 @@
         <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:18</v>
+        <v>2:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Em Beihold</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:50</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Michael Bublé</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:24</v>
+        <v>2:39</v>
       </c>
       <c r="H69" t="str">
-        <v>MyKey</v>
+        <v>kenzie</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:36</v>
+        <v>3:52</v>
       </c>
       <c r="H70" t="str">
-        <v>Max McNown</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H71" t="str">
-        <v>Megan Moroney</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H72" t="str">
-        <v>ERNEST</v>
+        <v>CHESCA</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H73" t="str">
-        <v>Bruno Mars</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:22</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>BLACKPINK</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:49</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Y2K</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-08</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:47</v>
+        <v>2:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Nessa Barrett</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-08</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:20</v>
+        <v>6:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Towa Bird</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:18</v>
+        <v>2:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Ty Myers</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:39</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>kenzie</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Leanna Crawford</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:01</v>
+        <v>2:59</v>
       </c>
       <c r="H81" t="str">
-        <v>Bryan Adams</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:54</v>
+        <v>2:22</v>
       </c>
       <c r="H82" t="str">
-        <v>CHESCA</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:03</v>
+        <v>3:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Roxette</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:50</v>
+        <v>2:28</v>
       </c>
       <c r="H84" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:06</v>
+        <v>2:47</v>
       </c>
       <c r="H85" t="str">
-        <v>Y2K</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:43</v>
+        <v>3:40</v>
       </c>
       <c r="H86" t="str">
-        <v>Lainey Wilson</v>
+        <v>Laufey</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>6:21</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Ava Max</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:46</v>
+        <v>4:49</v>
       </c>
       <c r="H88" t="str">
-        <v>Bryan Ferry</v>
+        <v>U2</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:42</v>
+        <v>3:35</v>
       </c>
       <c r="H89" t="str">
-        <v>Saint Harison</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Catie Turner</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:22</v>
+        <v>3:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Roxette</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:28</v>
+        <v>5:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Marcin</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:47</v>
+        <v>4:39</v>
       </c>
       <c r="H95" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:40</v>
       </c>
       <c r="H96" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:49</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Ava Max</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B98" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H98" t="str">
-        <v>U2</v>
+        <v>070 Shake</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-08</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H99" t="str">
-        <v>Taylor Swift</v>
+        <v>georgemichael</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-08</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:59</v>
+        <v>5:52</v>
       </c>
       <c r="H100" t="str">
-        <v>Kiana Ledé</v>
+        <v>georgemichael</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-08</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:38</v>
+        <v>3:22</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>American Girls</v>
       </c>
       <c r="B102" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>12 days ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>3:46</v>
+        <v>3:33</v>
       </c>
       <c r="H102" t="str">
-        <v>Madison Beer</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B103" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>12 days ago</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:08</v>
+        <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Sean Stemaly</v>
+        <v>Shakira</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L103" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>New Religion</v>
       </c>
       <c r="B104" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>13 days ago</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>5:32</v>
+        <v>2:54</v>
       </c>
       <c r="H104" t="str">
-        <v>earMUSIC</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L104" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B105" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>13 days ago</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:39</v>
+        <v>2:56</v>
       </c>
       <c r="H105" t="str">
-        <v>georgemichael</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L105" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B106" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>13 days ago</v>
+        <v>Ö</v>
       </c>
       <c r="G106" t="str">
-        <v>3:40</v>
+        <v>2:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Fcukers</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L106" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:57</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Self Esteem</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L107" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Berghain (Remix)</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Berghain (Remix) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H108" t="str">
-        <v>070 Shake</v>
+        <v>Conrad Taylor</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/conrad-taylor/193729134</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/berghain-remix/1883156562</v>
       </c>
       <c r="L108" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Berghain (Remix) - Conrad Taylor</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G109" t="str">
-        <v>4:49</v>
+        <v>2:24</v>
       </c>
       <c r="H109" t="str">
-        <v>georgemichael</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L109" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Medicine</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>5:52</v>
+        <v>2:34</v>
       </c>
       <c r="H110" t="str">
-        <v>georgemichael</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L110" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G111" t="str">
-        <v>3:22</v>
+        <v>4:11</v>
       </c>
       <c r="H111" t="str">
-        <v>Foo Fighters</v>
+        <v>TOMORA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L111" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>American Girls</v>
+        <v>Dog</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Torn</v>
       </c>
       <c r="G112" t="str">
-        <v>3:33</v>
+        <v>2:37</v>
       </c>
       <c r="H112" t="str">
-        <v>Harry Styles</v>
+        <v>Cobrah</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L112" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ALGO TÚ</v>
+        <v>Dance No More</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G113" t="str">
-        <v>3:33</v>
+        <v>3:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Shakira</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L113" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>New Religion</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>New Religion - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:54</v>
+        <v>3:09</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L114" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Where Do We Go</v>
+        <v>Tweak</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:56</v>
+        <v>2:28</v>
       </c>
       <c r="H115" t="str">
-        <v>Ayra Starr</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L115" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ö</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:51</v>
+        <v>3:05</v>
       </c>
       <c r="H116" t="str">
-        <v>Fcukers</v>
+        <v>aespa</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L116" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>We Don’t Get Along</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:29</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>Juice WRLD</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L117" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>bad bitch alert</v>
+        <v>Kerosene</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:24</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>The Warning</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L118" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Medicine</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Medicine - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:34</v>
+        <v>3:28</v>
       </c>
       <c r="H119" t="str">
-        <v>Channel Tres</v>
+        <v>J Balvin</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L119" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>COME CLOSER</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:11</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>TOMORA</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L120" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Dog</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Torn</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G121" t="str">
-        <v>2:37</v>
+        <v>3:20</v>
       </c>
       <c r="H121" t="str">
-        <v>Cobrah</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L121" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Dance No More</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-08</v>
@@ -5014,7 +5014,7 @@
         <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G122" t="str">
-        <v>3:14</v>
+        <v>4:08</v>
       </c>
       <c r="H122" t="str">
         <v>Harry Styles</v>
@@ -5026,21 +5026,21 @@
         <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L122" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>4:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Anne Hathaway</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L123" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tweak</v>
+        <v>Feel Better</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tweak - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:28</v>
+        <v>3:46</v>
       </c>
       <c r="H124" t="str">
-        <v>GIRLSET</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L124" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ATTITUDE</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G125" t="str">
-        <v>3:05</v>
+        <v>4:02</v>
       </c>
       <c r="H125" t="str">
-        <v>aespa</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L125" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Blame Texas</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Blame Texas - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:12</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Cody Johnson</v>
+        <v>Anitta</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L126" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Kerosene</v>
+        <v>San Charly</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Kerosene - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:26</v>
+        <v>2:54</v>
       </c>
       <c r="H127" t="str">
-        <v>The Warning</v>
+        <v>Xavi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L127" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G128" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H128" t="str">
-        <v>J Balvin</v>
+        <v>Juanes</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L128" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Save Me Tonight</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>4:20</v>
       </c>
       <c r="H129" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Fred again..</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L129" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Universal Soldier</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>HELP(2)</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G130" t="str">
-        <v>3:20</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Depeche Mode</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L130" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Coming Up Roses</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Atlanta</v>
       </c>
       <c r="G131" t="str">
-        <v>4:08</v>
+        <v>3:07</v>
       </c>
       <c r="H131" t="str">
-        <v>Harry Styles</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L131" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G132" t="str">
-        <v>4:43</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Noah Cyrus</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L132" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Feel Better</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Jean</v>
       </c>
       <c r="G133" t="str">
-        <v>3:46</v>
+        <v>3:04</v>
       </c>
       <c r="H133" t="str">
-        <v>Koe Wetzel</v>
+        <v>Yebba</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L133" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>400 Cities</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G134" t="str">
-        <v>4:02</v>
+        <v>2:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L134" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:14</v>
+        <v>3:19</v>
       </c>
       <c r="H135" t="str">
-        <v>Anitta</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L135" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>San Charly</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>San Charly - Single</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:54</v>
+        <v>3:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Xavi</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L136" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Timelapse de Sol</v>
+        <v>BREEZER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>JuanesTeban</v>
+        <v>Lost on You</v>
       </c>
       <c r="G137" t="str">
-        <v>3:05</v>
+        <v>3:30</v>
       </c>
       <c r="H137" t="str">
-        <v>Juanes</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L137" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>War To Love</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>USB002 REMIXES</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G138" t="str">
-        <v>4:20</v>
+        <v>3:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Fred again..</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L138" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>It’s Been Too Long</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Long Long Road</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:42</v>
+        <v>2:53</v>
       </c>
       <c r="H139" t="str">
-        <v>Ringo Starr</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L139" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Atlanta</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G140" t="str">
-        <v>3:07</v>
+        <v>3:34</v>
       </c>
       <c r="H140" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L140" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Devil You Know</v>
+        <v>Angel</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:10</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Maya Hawke</v>
+        <v>December 10</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L141" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Jean</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H142" t="str">
-        <v>Yebba</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L142" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>400 Cities</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Miracle Mile</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:17</v>
+        <v>2:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Paul Russell</v>
+        <v>ili</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L143" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>THE BOXER</v>
+        <v>Bleed</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>THE BOXER - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G144" t="str">
-        <v>3:19</v>
+        <v>3:40</v>
       </c>
       <c r="H144" t="str">
-        <v>Kids That Fly</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L144" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Borrowed Time</v>
+        <v>Die for You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G145" t="str">
-        <v>3:49</v>
+        <v>3:27</v>
       </c>
       <c r="H145" t="str">
-        <v>Sam Barber</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L145" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>BREEZER</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Lost on You</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:30</v>
+        <v>3:35</v>
       </c>
       <c r="H146" t="str">
-        <v>Tigers Jaw</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L146" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>War To Love</v>
+        <v>Wish</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Tragic Magic</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:46</v>
+        <v>2:45</v>
       </c>
       <c r="H147" t="str">
-        <v>Matt Corby</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L147" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Incompatibles</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:53</v>
+        <v>2:46</v>
       </c>
       <c r="H148" t="str">
-        <v>Christian Nodal</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L148" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Oídos Sordos</v>
+        <v>Fantasy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Metamorfosis</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:34</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Omarion</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L149" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Angel</v>
+        <v>why am i like this</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Angel - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H150" t="str">
-        <v>December 10</v>
+        <v>bbno$</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L150" t="str">
-        <v>Angel - December 10</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Trust Myself</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:03</v>
+        <v>2:55</v>
       </c>
       <c r="H151" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L151" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tears Ago</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Tears Ago - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G152" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>ili</v>
+        <v>15 15</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L152" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Bleed</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>House of Cards</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G153" t="str">
-        <v>3:40</v>
+        <v>3:13</v>
       </c>
       <c r="H153" t="str">
-        <v>The Amity Affliction</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L153" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Die for You</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Reflections</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G154" t="str">
-        <v>3:27</v>
+        <v>4:06</v>
       </c>
       <c r="H154" t="str">
-        <v>From Ashes to New</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L154" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:35</v>
+        <v>2:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Honey Dijon</v>
+        <v>aron!</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L155" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Wish</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Wish - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:45</v>
+        <v>3:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Cash Cobain</v>
+        <v>almost monday</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L156" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Clean Up Song</v>
+        <v>You and Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G157" t="str">
         <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>Tessa Violet</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L157" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Fantasy</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Fantasy - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:42</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Omarion</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L158" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>why am i like this</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>why am i like this - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:56</v>
+        <v>3:31</v>
       </c>
       <c r="H159" t="str">
-        <v>bbno$</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L159" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>How the Fire Started</v>
+        <v>DELETED</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>3:24</v>
       </c>
       <c r="H160" t="str">
-        <v>Eric Nam</v>
+        <v>vaultboy</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L160" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Take Off Late</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Mārara</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H161" t="str">
-        <v>15 15</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L161" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>With No Due Respect</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:13</v>
+        <v>5:29</v>
       </c>
       <c r="H162" t="str">
-        <v>Foggieraw</v>
+        <v>Kaskade</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L162" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G163" t="str">
-        <v>4:06</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Denzel Curry</v>
+        <v>MORGXN</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L163" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Wonderful Thing</v>
+        <v>To Myself</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G164" t="str">
-        <v>2:14</v>
+        <v>3:40</v>
       </c>
       <c r="H164" t="str">
-        <v>aron!</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L164" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>leaving is easy</v>
+        <v>TABOO</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>leaving is easy - Single</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:33</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>almost monday</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L165" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>You and Me</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>You and Me - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:46</v>
+        <v>2:52</v>
       </c>
       <c r="H166" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Two Friends</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L166" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>Be Mine</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:39</v>
+        <v>1:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Lily Meola</v>
+        <v>James Hype</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L167" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Everything to Nothing</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H168" t="str">
-        <v>Michael Sanzone</v>
+        <v>ANOTR</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L168" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>DELETED</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>DELETED - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G169" t="str">
         <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>vaultboy</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L169" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>A Thousand Years</v>
+        <v>Still Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:00</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>John Michael Howell</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L170" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:29</v>
+        <v>2:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Kaskade</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L171" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Havin'</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:16</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>MORGXN</v>
+        <v>1K Phew</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L172" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>To Myself</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>MINDFIELDS</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G173" t="str">
-        <v>3:40</v>
+        <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Alicia Creti</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L173" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>TABOO</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>TABOO - Single</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:45</v>
+        <v>3:16</v>
       </c>
       <c r="H174" t="str">
-        <v>Isaiah Falls</v>
+        <v>Juanchito</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L174" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:52</v>
+        <v>2:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Two Friends</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L175" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Be Mine</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Be Mine - Single</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>1:53</v>
+        <v>3:07</v>
       </c>
       <c r="H176" t="str">
-        <v>James Hype</v>
+        <v>Ama</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L176" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G177" t="str">
-        <v>3:11</v>
+        <v>4:24</v>
       </c>
       <c r="H177" t="str">
-        <v>ANOTR</v>
+        <v>Metric</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L177" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Evil Against Me</v>
+        <v>NOISE</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:42</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaya Zamora</v>
+        <v>ivri</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L178" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Still Do</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Still Do - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G179" t="str">
-        <v>3:03</v>
+        <v>4:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Anne Wilson</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L179" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DIE 4 ME</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:37</v>
+        <v>4:24</v>
       </c>
       <c r="H180" t="str">
-        <v>Taylor Hill</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L180" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Havin'</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Havin' - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:49</v>
+        <v>3:46</v>
       </c>
       <c r="H181" t="str">
-        <v>1K Phew</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L181" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Good Friend</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Singing</v>
       </c>
       <c r="G182" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Carolina Ross</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L182" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Mi Amante</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mi Amante - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:16</v>
+        <v>2:52</v>
       </c>
       <c r="H183" t="str">
-        <v>Juanchito</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L183" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Ay Pequeña</v>
+        <v>Tellme</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:00</v>
+        <v>3:04</v>
       </c>
       <c r="H184" t="str">
-        <v>Flavia Laos</v>
+        <v>Joon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L184" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Need it Bad</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Need it Bad - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:07</v>
+        <v>4:07</v>
       </c>
       <c r="H185" t="str">
-        <v>Ama</v>
+        <v>zzzahara</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L185" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Time Is A Bomb</v>
+        <v>Soren</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:24</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Metric</v>
+        <v>Orca</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L186" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>NOISE</v>
+        <v>Gloria</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>NOISE - Single</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G187" t="str">
-        <v>2:42</v>
+        <v>3:24</v>
       </c>
       <c r="H187" t="str">
-        <v>ivri</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L187" t="str">
-        <v>NOISE - ivri</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Prairie</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G188" t="str">
-        <v>4:46</v>
+        <v>4:59</v>
       </c>
       <c r="H188" t="str">
-        <v>Bike Routes</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L188" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bird Eye View</v>
+        <v>Tough</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:24</v>
+        <v>3:15</v>
       </c>
       <c r="H189" t="str">
-        <v>Hayden Everett</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L189" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:46</v>
+        <v>1:08</v>
       </c>
       <c r="H190" t="str">
-        <v>Erin Rae</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L190" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Good Friend</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Singing</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:39</v>
+        <v>4:08</v>
       </c>
       <c r="H191" t="str">
-        <v>Gia Margaret</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L191" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H192" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L192" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Tellme</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Tellme - Single</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G193" t="str">
         <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>Joon</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L193" t="str">
-        <v>Tellme - Joon</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>I Can Be Yours</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G194" t="str">
-        <v>4:07</v>
+        <v>3:12</v>
       </c>
       <c r="H194" t="str">
-        <v>zzzahara</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L194" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Soren</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Soren - Single</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H195" t="str">
-        <v>Orca</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L195" t="str">
-        <v>Soren - Orca</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Gloria</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Guesthouse</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G196" t="str">
-        <v>3:24</v>
+        <v>3:30</v>
       </c>
       <c r="H196" t="str">
-        <v>Shai Maestro</v>
+        <v>ERRA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L196" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Gemini Eyes</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-08</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>The Crawl</v>
       </c>
       <c r="G197" t="str">
-        <v>4:59</v>
+        <v>5:12</v>
       </c>
       <c r="H197" t="str">
-        <v>Arima Ederra</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L197" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Tough</v>
+        <v>Lay Down Your Soul</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-08</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Tough - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G198" t="str">
-        <v>3:15</v>
+        <v>3:13</v>
       </c>
       <c r="H198" t="str">
-        <v>Nia Smith</v>
+        <v>Venom</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
       </c>
       <c r="L198" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>Lay Down Your Soul - Venom</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>NO HOOK</v>
+        <v>Ghost Notes</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-08</v>
@@ -7937,372 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>NO HOOK - Single</v>
+        <v>Slave Machine</v>
       </c>
       <c r="G199" t="str">
-        <v>1:08</v>
+        <v>4:27</v>
       </c>
       <c r="H199" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Nervosa</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
       <c r="L199" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>4:08</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Rosie Bennet</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
-      </c>
-      <c r="L200" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Mean 2 Me</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Mean 2 Me - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>4:27</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Skyla Tylaa</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>CAPTAIN KERNEL</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>BIG MAMA</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Flying Lotus</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
-      </c>
-      <c r="L202" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Nothings What It Seems</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Midwest Memoir</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Tyler Nance</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>No Need For Leavin'</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>No Need For Leavin' - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Kameron Marlowe</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
-      </c>
-      <c r="L204" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>ii. in the gut of the wolf</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>silence outlives the earth</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:30</v>
-      </c>
-      <c r="H205" t="str">
-        <v>ERRA</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
-      </c>
-      <c r="L205" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Poison Icon</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>The Crawl</v>
-      </c>
-      <c r="G206" t="str">
-        <v>5:12</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Temple of Void</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Poison Icon - Temple of Void</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Lay Down Your Soul</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Into Oblivion</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:13</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Venom</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Lay Down Your Soul - Venom</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Ghost Notes</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Slave Machine</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:27</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Nervosa</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
-      </c>
-      <c r="L208" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -1655,7 +1655,7 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:52</v>
@@ -2111,7 +2111,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:50</v>
@@ -3137,7 +3137,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:03</v>
@@ -3821,7 +3821,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>4:38</v>

--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,19 +515,19 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,19 +553,19 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:43</v>
@@ -1275,19 +1275,19 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>4:43</v>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>4:37</v>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:10</v>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>Streamed 7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Streamed 6 days ago</v>
+        <v>Streamed 7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>27:54:45</v>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>7:20</v>
@@ -1883,19 +1883,19 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:01</v>
@@ -1921,19 +1921,19 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:31</v>
@@ -1959,19 +1959,19 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:00</v>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:32</v>
@@ -2073,19 +2073,19 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>5:03</v>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>6:21</v>
@@ -3327,19 +3327,19 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>2:46</v>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:35</v>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -819,7 +819,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:41</v>
@@ -857,7 +857,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:29</v>
@@ -895,7 +895,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:43</v>
@@ -933,7 +933,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:46</v>
@@ -971,7 +971,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:01</v>
@@ -1009,7 +1009,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:23</v>
@@ -1047,7 +1047,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:39</v>
@@ -1085,7 +1085,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:04</v>
@@ -1123,7 +1123,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:25</v>
@@ -1161,7 +1161,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:49</v>
@@ -1199,7 +1199,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:14</v>
@@ -1807,7 +1807,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>5:18</v>
@@ -2529,7 +2529,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:18</v>
@@ -2567,7 +2567,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:50</v>
@@ -2605,7 +2605,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:24</v>
@@ -2643,7 +2643,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:36</v>
@@ -2681,7 +2681,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:34</v>
@@ -2719,7 +2719,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:03</v>
@@ -2757,7 +2757,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:31</v>
@@ -2795,7 +2795,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:22</v>
@@ -2833,7 +2833,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>5:49</v>
@@ -2871,7 +2871,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:47</v>
@@ -2909,7 +2909,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:20</v>
@@ -2947,7 +2947,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:18</v>
@@ -2985,7 +2985,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:39</v>
@@ -3023,7 +3023,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:52</v>
@@ -3061,7 +3061,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:01</v>
@@ -3099,7 +3099,7 @@
         <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:54</v>
@@ -3213,7 +3213,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:06</v>
@@ -3251,7 +3251,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>2:43</v>
@@ -3631,7 +3631,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:40</v>
@@ -3669,7 +3669,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>2:49</v>

--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-09</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
       </c>
       <c r="G2" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-09</v>
@@ -492,10 +492,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H3" t="str">
-        <v>Warner Records</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-09</v>
@@ -530,10 +530,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H4" t="str">
-        <v>Ellise</v>
+        <v>Warner Records</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-09</v>
@@ -568,10 +568,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H5" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-09</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-09</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H7" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-09</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H8" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-09</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H9" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-09</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H10" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-09</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-09</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-09</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-09</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-09</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-09</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-09</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-09</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-09</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H19" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-09</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H20" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-09</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-09</v>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-09</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H23" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-09</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-09</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-09</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H26" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-09</v>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-09</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-09</v>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-09</v>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H30" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-09</v>
@@ -1556,10 +1556,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H31" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-09</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-09</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-09</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-09</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H35" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-09</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>Streamed 7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Streamed 7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>27:54:45</v>
+        <v>4:30</v>
       </c>
       <c r="H37" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>Streamed 7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-09</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>Streamed 7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:18</v>
+        <v>27:54:45</v>
       </c>
       <c r="H38" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-09</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-09</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H40" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B41" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-09</v>
@@ -1936,10 +1936,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-09</v>
@@ -1974,10 +1974,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B43" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-09</v>
@@ -2012,10 +2012,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H43" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-09</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-09</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-09</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H46" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-09</v>
@@ -2164,10 +2164,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-09</v>
@@ -2202,10 +2202,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H48" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-09</v>
@@ -2240,10 +2240,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H49" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-09</v>
@@ -2278,10 +2278,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-09</v>
@@ -2316,10 +2316,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-09</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-09</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H53" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-09</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H54" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-09</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-09</v>
@@ -2544,10 +2544,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B58" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-09</v>
@@ -2582,10 +2582,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H58" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-09</v>
@@ -2620,10 +2620,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H59" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B60" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-09</v>
@@ -2658,10 +2658,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-09</v>
@@ -2696,10 +2696,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H61" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-09</v>
@@ -2734,10 +2734,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H62" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-09</v>
@@ -2772,10 +2772,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H63" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B64" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-09</v>
@@ -2810,10 +2810,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B65" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-09</v>
@@ -2848,10 +2848,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B66" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-09</v>
@@ -2886,10 +2886,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-09</v>
@@ -2924,10 +2924,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H67" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-09</v>
@@ -2962,10 +2962,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H68" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-09</v>
@@ -3000,10 +3000,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-09</v>
@@ -3038,10 +3038,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-09</v>
@@ -3076,10 +3076,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H71" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B72" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-09</v>
@@ -3114,10 +3114,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H72" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B73" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-09</v>
@@ -3152,10 +3152,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-09</v>
@@ -3190,10 +3190,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H74" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-09</v>
@@ -3266,10 +3266,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B77" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-09</v>
@@ -3304,10 +3304,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B78" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-09</v>
@@ -3342,10 +3342,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B79" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-09</v>
@@ -3380,10 +3380,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B80" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-09</v>
@@ -3418,10 +3418,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H80" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-09</v>
@@ -3456,10 +3456,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H81" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-09</v>
@@ -3494,10 +3494,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H82" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B83" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-09</v>
@@ -3532,10 +3532,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H83" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B84" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-09</v>
@@ -3570,10 +3570,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-09</v>
@@ -3646,10 +3646,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H86" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B87" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-09</v>
@@ -3684,10 +3684,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H87" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-09</v>
@@ -3722,10 +3722,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H88" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B89" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-09</v>
@@ -3760,10 +3760,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H90" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H91" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-09</v>
@@ -3874,10 +3874,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B93" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-09</v>
@@ -3912,10 +3912,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-09</v>
@@ -3950,10 +3950,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H94" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H96" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-09</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-09</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-09</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H99" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-09</v>
@@ -4178,7 +4178,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H100" t="str">
         <v>georgemichael</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-09</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H101" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>American Girls</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-09</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:33</v>
+        <v>3:22</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ALGO TÚ</v>
+        <v>American Girls</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
         <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Shakira</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>New Religion</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>New Religion - Single</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:54</v>
+        <v>3:33</v>
       </c>
       <c r="H104" t="str">
-        <v>Bebe Rexha</v>
+        <v>Shakira</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L104" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Where Do We Go</v>
+        <v>New Religion</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:56</v>
+        <v>2:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Ayra Starr</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L105" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ö</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H106" t="str">
-        <v>Fcukers</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L106" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>We Don’t Get Along</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>2:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Juice WRLD</v>
+        <v>Fcukers</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L107" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Berghain (Remix)</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Berghain (Remix) - Single</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Conrad Taylor</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/conrad-taylor/193729134</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/berghain-remix/1883156562</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L108" t="str">
-        <v>Berghain (Remix) - Conrad Taylor</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>bad bitch alert</v>
+        <v>Berghain (Remix)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Berghain (Remix) - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:24</v>
+        <v>2:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/berghain-remix/1883156562</v>
       </c>
       <c r="L109" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>Berghain (Remix) - ROSALÍA</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Medicine</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Medicine - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G110" t="str">
-        <v>2:34</v>
+        <v>2:24</v>
       </c>
       <c r="H110" t="str">
-        <v>Channel Tres</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L110" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H111" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L111" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G112" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H112" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L112" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dance No More</v>
+        <v>Dog</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Torn</v>
       </c>
       <c r="G113" t="str">
-        <v>3:14</v>
+        <v>2:37</v>
       </c>
       <c r="H113" t="str">
-        <v>Harry Styles</v>
+        <v>Cobrah</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L113" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Dance No More</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G114" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Anne Hathaway</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L114" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tweak</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tweak - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:28</v>
+        <v>3:09</v>
       </c>
       <c r="H115" t="str">
-        <v>GIRLSET</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L115" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ATTITUDE</v>
+        <v>Tweak</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:05</v>
+        <v>2:28</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L116" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blame Texas</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Blame Texas - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H117" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L117" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Kerosene</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Kerosene - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H118" t="str">
-        <v>The Warning</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L118" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Kerosene</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:28</v>
+        <v>3:26</v>
       </c>
       <c r="H119" t="str">
-        <v>J Balvin</v>
+        <v>The Warning</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L119" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Save Me Tonight</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:28</v>
       </c>
       <c r="H120" t="str">
-        <v>Jennifer Lopez</v>
+        <v>J Balvin</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L120" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Universal Soldier</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>HELP(2)</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:20</v>
+        <v>3:16</v>
       </c>
       <c r="H121" t="str">
-        <v>Depeche Mode</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L121" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Coming Up Roses</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G122" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H122" t="str">
-        <v>Harry Styles</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L122" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G123" t="str">
-        <v>4:43</v>
+        <v>4:08</v>
       </c>
       <c r="H123" t="str">
-        <v>Noah Cyrus</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L123" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Feel Better</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:46</v>
+        <v>4:43</v>
       </c>
       <c r="H124" t="str">
-        <v>Koe Wetzel</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L124" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Feel Better</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>4:02</v>
+        <v>3:46</v>
       </c>
       <c r="H125" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L125" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>4:02</v>
       </c>
       <c r="H126" t="str">
-        <v>Anitta</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L126" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>San Charly</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>San Charly - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:54</v>
+        <v>2:14</v>
       </c>
       <c r="H127" t="str">
-        <v>Xavi</v>
+        <v>Anitta</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L127" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Timelapse de Sol</v>
+        <v>San Charly</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>JuanesTeban</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H128" t="str">
-        <v>Juanes</v>
+        <v>Xavi</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L128" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>USB002 REMIXES</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G129" t="str">
-        <v>4:20</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Fred again..</v>
+        <v>Juanes</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L129" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>It’s Been Too Long</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Long Long Road</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>4:20</v>
       </c>
       <c r="H130" t="str">
-        <v>Ringo Starr</v>
+        <v>Fred again..</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L130" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Atlanta</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G131" t="str">
-        <v>3:07</v>
+        <v>2:42</v>
       </c>
       <c r="H131" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L131" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Devil You Know</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Atlanta</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>3:07</v>
       </c>
       <c r="H132" t="str">
-        <v>Maya Hawke</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L132" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Jean</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G133" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H133" t="str">
-        <v>Yebba</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L133" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>400 Cities</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Miracle Mile</v>
+        <v>Jean</v>
       </c>
       <c r="G134" t="str">
-        <v>2:17</v>
+        <v>3:04</v>
       </c>
       <c r="H134" t="str">
-        <v>Paul Russell</v>
+        <v>Yebba</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L134" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>THE BOXER</v>
+        <v>400 Cities</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>THE BOXER - Single</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G135" t="str">
-        <v>3:19</v>
+        <v>2:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Kids That Fly</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L135" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Borrowed Time</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:49</v>
+        <v>3:19</v>
       </c>
       <c r="H136" t="str">
-        <v>Sam Barber</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L136" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BREEZER</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Lost on You</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:30</v>
+        <v>3:49</v>
       </c>
       <c r="H137" t="str">
-        <v>Tigers Jaw</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L137" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>War To Love</v>
+        <v>BREEZER</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Tragic Magic</v>
+        <v>Lost on You</v>
       </c>
       <c r="G138" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H138" t="str">
-        <v>Matt Corby</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L138" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Incompatibles</v>
+        <v>War To Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G139" t="str">
-        <v>2:53</v>
+        <v>3:46</v>
       </c>
       <c r="H139" t="str">
-        <v>Christian Nodal</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L139" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Oídos Sordos</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Metamorfosis</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H140" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L140" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Angel</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Angel - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>December 10</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L141" t="str">
-        <v>Angel - December 10</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Trust Myself</v>
+        <v>Angel</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:03</v>
+        <v>2:27</v>
       </c>
       <c r="H142" t="str">
-        <v>Katelyn Tarver</v>
+        <v>December 10</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L142" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Tears Ago</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Tears Ago - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G143" t="str">
-        <v>2:35</v>
+        <v>3:03</v>
       </c>
       <c r="H143" t="str">
-        <v>ili</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L143" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bleed</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>House of Cards</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:40</v>
+        <v>2:35</v>
       </c>
       <c r="H144" t="str">
-        <v>The Amity Affliction</v>
+        <v>ili</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L144" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Die for You</v>
+        <v>Bleed</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Reflections</v>
+        <v>House of Cards</v>
       </c>
       <c r="G145" t="str">
-        <v>3:27</v>
+        <v>3:40</v>
       </c>
       <c r="H145" t="str">
-        <v>From Ashes to New</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L145" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>Die for You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G146" t="str">
-        <v>3:35</v>
+        <v>3:27</v>
       </c>
       <c r="H146" t="str">
-        <v>Honey Dijon</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L146" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wish</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Wish - Single</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:45</v>
+        <v>3:35</v>
       </c>
       <c r="H147" t="str">
-        <v>Cash Cobain</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L147" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Clean Up Song</v>
+        <v>Wish</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:46</v>
+        <v>2:45</v>
       </c>
       <c r="H148" t="str">
-        <v>Tessa Violet</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L148" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Fantasy</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Fantasy - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H149" t="str">
-        <v>Omarion</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L149" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>why am i like this</v>
+        <v>Fantasy</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>why am i like this - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:56</v>
+        <v>3:42</v>
       </c>
       <c r="H150" t="str">
-        <v>bbno$</v>
+        <v>Omarion</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L150" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>How the Fire Started</v>
+        <v>why am i like this</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:55</v>
+        <v>2:56</v>
       </c>
       <c r="H151" t="str">
-        <v>Eric Nam</v>
+        <v>bbno$</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L151" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Take Off Late</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mārara</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>2:55</v>
       </c>
       <c r="H152" t="str">
-        <v>15 15</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L152" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>With No Due Respect</v>
+        <v>Mārara</v>
       </c>
       <c r="G153" t="str">
-        <v>3:13</v>
+        <v>3:23</v>
       </c>
       <c r="H153" t="str">
-        <v>Foggieraw</v>
+        <v>15 15</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L153" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G154" t="str">
-        <v>4:06</v>
+        <v>3:13</v>
       </c>
       <c r="H154" t="str">
-        <v>Denzel Curry</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L154" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Wonderful Thing</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G155" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H155" t="str">
-        <v>aron!</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L155" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>leaving is easy</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>leaving is easy - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:33</v>
+        <v>2:14</v>
       </c>
       <c r="H156" t="str">
-        <v>almost monday</v>
+        <v>aron!</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L156" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You and Me</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You and Me - Single</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H157" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>almost monday</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L157" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>You and Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>2:46</v>
       </c>
       <c r="H158" t="str">
-        <v>Lily Meola</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L158" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Everything to Nothing</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:31</v>
+        <v>2:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Michael Sanzone</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L159" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DELETED</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>DELETED - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H160" t="str">
-        <v>vaultboy</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L160" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>A Thousand Years</v>
+        <v>DELETED</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:00</v>
+        <v>3:24</v>
       </c>
       <c r="H161" t="str">
-        <v>John Michael Howell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L161" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>5:29</v>
+        <v>3:00</v>
       </c>
       <c r="H162" t="str">
-        <v>Kaskade</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L162" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>5:29</v>
       </c>
       <c r="H163" t="str">
-        <v>MORGXN</v>
+        <v>Kaskade</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L163" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To Myself</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>MINDFIELDS</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G164" t="str">
-        <v>3:40</v>
+        <v>3:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Alicia Creti</v>
+        <v>MORGXN</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L164" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>TABOO</v>
+        <v>To Myself</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>TABOO - Single</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G165" t="str">
-        <v>2:45</v>
+        <v>3:40</v>
       </c>
       <c r="H165" t="str">
-        <v>Isaiah Falls</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L165" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>TABOO</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:52</v>
+        <v>2:45</v>
       </c>
       <c r="H166" t="str">
-        <v>Two Friends</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L166" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Be Mine</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Be Mine - Single</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>1:53</v>
+        <v>2:52</v>
       </c>
       <c r="H167" t="str">
-        <v>James Hype</v>
+        <v>Two Friends</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L167" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Be Mine</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:11</v>
+        <v>1:53</v>
       </c>
       <c r="H168" t="str">
-        <v>ANOTR</v>
+        <v>James Hype</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L168" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Evil Against Me</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:11</v>
       </c>
       <c r="H169" t="str">
-        <v>Shaya Zamora</v>
+        <v>ANOTR</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L169" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Still Do</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Still Do - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>3:24</v>
       </c>
       <c r="H170" t="str">
-        <v>Anne Wilson</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L170" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>DIE 4 ME</v>
+        <v>Still Do</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>3:03</v>
       </c>
       <c r="H171" t="str">
-        <v>Taylor Hill</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L171" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Havin'</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Havin' - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>2:37</v>
       </c>
       <c r="H172" t="str">
-        <v>1K Phew</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/havin/1878165149</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L172" t="str">
-        <v>Havin' - 1K Phew</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Se Me Va A Pasar</v>
+        <v>Havin'</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Coleccionando Corazones</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:16</v>
+        <v>2:49</v>
       </c>
       <c r="H173" t="str">
-        <v>Carolina Ross</v>
+        <v>1K Phew</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L173" t="str">
-        <v>Se Me Va A Pasar - Carolina Ross</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Mi Amante</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Mi Amante - Single</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G174" t="str">
         <v>3:16</v>
       </c>
       <c r="H174" t="str">
-        <v>Juanchito</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L174" t="str">
-        <v>Mi Amante - Juanchito</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Ay Pequeña</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Rubia Enamorada - EP</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:00</v>
+        <v>3:16</v>
       </c>
       <c r="H175" t="str">
-        <v>Flavia Laos</v>
+        <v>Juanchito</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L175" t="str">
-        <v>Ay Pequeña - Flavia Laos</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Need it Bad</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Need it Bad - Single</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G176" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H176" t="str">
-        <v>Ama</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L176" t="str">
-        <v>Need it Bad - Ama</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Time Is A Bomb</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:24</v>
+        <v>3:07</v>
       </c>
       <c r="H177" t="str">
-        <v>Metric</v>
+        <v>Ama</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L177" t="str">
-        <v>Time Is A Bomb - Metric</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>NOISE</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/noise/1878401282</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>NOISE - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G178" t="str">
-        <v>2:42</v>
+        <v>4:24</v>
       </c>
       <c r="H178" t="str">
-        <v>ivri</v>
+        <v>Metric</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/noise/1878401279</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L178" t="str">
-        <v>NOISE - ivri</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Delicate (feat. Jake Clemons)</v>
+        <v>NOISE</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Prairie</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:46</v>
+        <v>2:42</v>
       </c>
       <c r="H179" t="str">
-        <v>Bike Routes</v>
+        <v>ivri</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L179" t="str">
-        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bird Eye View</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Bird Eye View - Single</v>
+        <v>Prairie</v>
       </c>
       <c r="G180" t="str">
-        <v>4:24</v>
+        <v>4:46</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L180" t="str">
-        <v>Bird Eye View - Hayden Everett</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Whip-Poor-Will</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Whip-Poor-Will - Single</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>4:24</v>
       </c>
       <c r="H181" t="str">
-        <v>Erin Rae</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L181" t="str">
-        <v>Whip-Poor-Will - Erin Rae</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Good Friend</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Singing</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>3:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Gia Margaret</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L182" t="str">
-        <v>Good Friend - Gia Margaret</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>NEVER BE THE SAME</v>
+        <v>Good Friend</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>NEVER BE THE SAME - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G183" t="str">
-        <v>2:52</v>
+        <v>3:39</v>
       </c>
       <c r="H183" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L183" t="str">
-        <v>NEVER BE THE SAME - THEHONESTGUY</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tellme</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tellme/1880089949</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Tellme - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H184" t="str">
-        <v>Joon</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/joon/1515228137</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tellme/1880089948</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L184" t="str">
-        <v>Tellme - Joon</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>I Can Be Yours</v>
+        <v>Tellme</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>I Can Be Yours - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:07</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>zzzahara</v>
+        <v>Joon</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L185" t="str">
-        <v>I Can Be Yours - zzzahara</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Soren</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/soren/1876596568</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soren - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>4:07</v>
       </c>
       <c r="H186" t="str">
-        <v>Orca</v>
+        <v>zzzahara</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/soren/1876596567</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L186" t="str">
-        <v>Soren - Orca</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Gloria</v>
+        <v>Soren</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/gloria/1842363092</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Guesthouse</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:24</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Shai Maestro</v>
+        <v>Orca</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/gloria/1842362686</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L187" t="str">
-        <v>Gloria - Shai Maestro</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Gemini Eyes</v>
+        <v>Gloria</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>A Rush To Nowhere</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G188" t="str">
-        <v>4:59</v>
+        <v>3:24</v>
       </c>
       <c r="H188" t="str">
-        <v>Arima Ederra</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L188" t="str">
-        <v>Gemini Eyes - Arima Ederra</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Tough</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/tough/1878716666</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Tough - Single</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G189" t="str">
-        <v>3:15</v>
+        <v>4:59</v>
       </c>
       <c r="H189" t="str">
-        <v>Nia Smith</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/tough/1878716664</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L189" t="str">
-        <v>Tough - Nia Smith</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>NO HOOK</v>
+        <v>Tough</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>NO HOOK - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>1:08</v>
+        <v>3:15</v>
       </c>
       <c r="H190" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L190" t="str">
-        <v>NO HOOK - KARRAHBOOO</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:08</v>
+        <v>1:08</v>
       </c>
       <c r="H191" t="str">
-        <v>Rosie Bennet</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L191" t="str">
-        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Mean 2 Me</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Mean 2 Me - Single</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:27</v>
+        <v>4:08</v>
       </c>
       <c r="H192" t="str">
-        <v>Skyla Tylaa</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L192" t="str">
-        <v>Mean 2 Me - Skyla Tylaa</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CAPTAIN KERNEL</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-09</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>BIG MAMA</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>4:27</v>
       </c>
       <c r="H193" t="str">
-        <v>Flying Lotus</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L193" t="str">
-        <v>CAPTAIN KERNEL - Flying Lotus</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Nothings What It Seems</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-09</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Midwest Memoir</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G194" t="str">
-        <v>3:12</v>
+        <v>3:04</v>
       </c>
       <c r="H194" t="str">
-        <v>Tyler Nance</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L194" t="str">
-        <v>Nothings What It Seems - Tyler Nance</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>No Need For Leavin'</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-09</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>No Need For Leavin' - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G195" t="str">
-        <v>3:35</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L195" t="str">
-        <v>No Need For Leavin' - Kameron Marlowe</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ii. in the gut of the wolf</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-09</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>silence outlives the earth</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:30</v>
+        <v>3:35</v>
       </c>
       <c r="H196" t="str">
-        <v>ERRA</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/erra/408917738</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L196" t="str">
-        <v>ii. in the gut of the wolf - ERRA</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Poison Icon</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-09</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Crawl</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G197" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H197" t="str">
-        <v>Temple of Void</v>
+        <v>ERRA</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L197" t="str">
-        <v>Poison Icon - Temple of Void</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Lay Down Your Soul</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-09</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Into Oblivion</v>
+        <v>The Crawl</v>
       </c>
       <c r="G198" t="str">
-        <v>3:13</v>
+        <v>5:12</v>
       </c>
       <c r="H198" t="str">
-        <v>Venom</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L198" t="str">
-        <v>Lay Down Your Soul - Venom</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Lay Down Your Soul</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Lay Down Your Soul - Venom</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Ghost Notes</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Slave Machine</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>4:27</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>Nervosa</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week02/titles.xlsx
+++ b/data/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L219"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409931&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409930&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-09</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>דניאל זנדאני - יא יומה</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409929&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-09</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Warner Records</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
+        <v>דניאל זנדאני - יא יומה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>פיקאסו - מתערבב לי</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409928&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-09</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>2:33</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Ellise</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>פיקאסו - מתערבב לי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>עמרי וקנין - שיר שלא נגמר</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409927&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-09</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>5:01</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>The Doobie Brothers</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>עמרי וקנין - שיר שלא נגמר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>נעם שפייר - כנות</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409926&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-09</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>4:56</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>נעם שפייר - כנות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>ישי ריבו - הנשמה לא Meta</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409925&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-09</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>2:54</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Bebe Rexha</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>ישי ריבו - הנשמה לא Meta</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409924&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-09</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>2:46</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>NathanEvanss</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>יונתן שחר - דרך לחזור</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409923&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-09</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>R3HAB</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>יונתן שחר - דרך לחזור</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409922&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-09</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>יובל אבידן - ברוך השם אני טוב</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409921&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-09</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>3:16</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>יובל אבידן - ברוך השם אני טוב</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>חני מסלה - פאבלות</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409920&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-09</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Johnny Orlando</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>חני מסלה - פאבלות</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>הילה גדסי - רק אתה יודע</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409919&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-09</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>2:29</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Russell Dickerson</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>הילה גדסי - רק אתה יודע</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>האחים בכר - נשאר הגעגוע</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409918&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-09</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>2:43</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>האחים בכר - נשאר הגעגוע</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>דניאל כהן - ימים של גאולה</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409917&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-09</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>3:46</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Matt Hansen</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>דניאל כהן - ימים של גאולה</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409916&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-09</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Mike Posner</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409915&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-09</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>3:23</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>Katelyn Tarver</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409914&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-09</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>3:39</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>בן זוהר - טיל</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409913&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-09</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>בן זוהר - טיל</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-09</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:25</v>
+        <v>3:48</v>
       </c>
       <c r="H21" t="str">
-        <v>vaultboy</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-09</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>4:58</v>
       </c>
       <c r="H22" t="str">
-        <v>The Warning</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-09</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:14</v>
+        <v>2:33</v>
       </c>
       <c r="H23" t="str">
-        <v>aron!</v>
+        <v>Ellise</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-09</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:43</v>
+        <v>5:01</v>
       </c>
       <c r="H24" t="str">
-        <v>Bazzi</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-09</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:43</v>
+        <v>4:56</v>
       </c>
       <c r="H25" t="str">
-        <v>Sting</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-09</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:44</v>
+        <v>2:54</v>
       </c>
       <c r="H26" t="str">
-        <v>Dean Lewis</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-09</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:37</v>
+        <v>2:46</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-09</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:52</v>
+        <v>2:56</v>
       </c>
       <c r="H28" t="str">
-        <v>Cannons</v>
+        <v>R3HAB</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-09</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:13</v>
+        <v>3:21</v>
       </c>
       <c r="H29" t="str">
-        <v>Kim Petras</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-09</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:19</v>
+        <v>3:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Vanessa Carlton</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-09</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:31</v>
+        <v>2:41</v>
       </c>
       <c r="H31" t="str">
-        <v>Kiana Ledé</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-09</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-09</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H33" t="str">
-        <v>Maya Hawke</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-09</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:55</v>
+        <v>3:46</v>
       </c>
       <c r="H34" t="str">
-        <v>Armin van Buuren</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-09</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H35" t="str">
-        <v>Demi Lovato</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-09</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:53</v>
+        <v>3:23</v>
       </c>
       <c r="H36" t="str">
-        <v>Peter Gabriel</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:30</v>
+        <v>3:39</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie J</v>
+        <v>almost monday</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>Streamed 7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-09</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Streamed 7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>27:54:45</v>
+        <v>3:04</v>
       </c>
       <c r="H38" t="str">
-        <v>BRITs</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-09</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:18</v>
+        <v>3:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Harry Styles</v>
+        <v>vaultboy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-09</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>7:20</v>
+        <v>3:49</v>
       </c>
       <c r="H40" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>The Warning</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-09</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H41" t="str">
-        <v>BRITs</v>
+        <v>aron!</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-09</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-09</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:00</v>
+        <v>4:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Sting</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-09</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:11</v>
+        <v>2:44</v>
       </c>
       <c r="H44" t="str">
-        <v>The Kiffness</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-09</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>4:37</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauv</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-09</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:03</v>
+        <v>4:52</v>
       </c>
       <c r="H46" t="str">
-        <v>RAYE</v>
+        <v>Cannons</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-09</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:50</v>
+        <v>2:13</v>
       </c>
       <c r="H47" t="str">
-        <v>Armik</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-09</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:53</v>
+        <v>3:19</v>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-09</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:04</v>
+        <v>2:31</v>
       </c>
       <c r="H49" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-09</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:32</v>
+        <v>2:43</v>
       </c>
       <c r="H50" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-09</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:47</v>
+        <v>3:10</v>
       </c>
       <c r="H51" t="str">
-        <v>Girl Tones</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-09</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>3:55</v>
       </c>
       <c r="H52" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-09</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H53" t="str">
-        <v>HAUSER</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-09</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:59</v>
+        <v>2:53</v>
       </c>
       <c r="H54" t="str">
-        <v>Queen Official</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:55</v>
+        <v>4:30</v>
       </c>
       <c r="H55" t="str">
-        <v>Tenille Townes</v>
+        <v>Jessie J</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:12</v>
+        <v>5:18</v>
       </c>
       <c r="H56" t="str">
-        <v>Self Esteem</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-09</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:47</v>
+        <v>7:20</v>
       </c>
       <c r="H57" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-09</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:18</v>
+        <v>3:01</v>
       </c>
       <c r="H58" t="str">
-        <v>Em Beihold</v>
+        <v>BRITs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-09</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:50</v>
+        <v>3:31</v>
       </c>
       <c r="H59" t="str">
-        <v>Michael Bublé</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-09</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H60" t="str">
-        <v>MyKey</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Max McNown</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:34</v>
+        <v>3:32</v>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>Lauv</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B63" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-09</v>
@@ -2772,10 +2772,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:03</v>
+        <v>5:03</v>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>RAYE</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B64" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-09</v>
@@ -2810,10 +2810,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>4:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Bruno Mars</v>
+        <v>Armik</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B65" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-09</v>
@@ -2848,10 +2848,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:22</v>
+        <v>4:53</v>
       </c>
       <c r="H65" t="str">
-        <v>BLACKPINK</v>
+        <v>Scorpions</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B66" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-09</v>
@@ -2886,10 +2886,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:49</v>
+        <v>3:04</v>
       </c>
       <c r="H66" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B67" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-09</v>
@@ -2924,10 +2924,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H67" t="str">
-        <v>Nessa Barrett</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-09</v>
@@ -2962,10 +2962,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-09</v>
@@ -3000,10 +3000,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:18</v>
+        <v>3:40</v>
       </c>
       <c r="H69" t="str">
-        <v>Ty Myers</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-09</v>
@@ -3038,10 +3038,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:39</v>
+        <v>4:05</v>
       </c>
       <c r="H70" t="str">
-        <v>kenzie</v>
+        <v>HAUSER</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-09</v>
@@ -3076,10 +3076,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:52</v>
+        <v>2:59</v>
       </c>
       <c r="H71" t="str">
-        <v>Leanna Crawford</v>
+        <v>Queen Official</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B72" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-09</v>
@@ -3114,10 +3114,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:01</v>
+        <v>3:55</v>
       </c>
       <c r="H72" t="str">
-        <v>Bryan Adams</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B73" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-09</v>
@@ -3152,10 +3152,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:54</v>
+        <v>5:12</v>
       </c>
       <c r="H73" t="str">
-        <v>CHESCA</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-09</v>
@@ -3190,10 +3190,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:03</v>
+        <v>3:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B75" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-09</v>
@@ -3228,10 +3228,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>3:18</v>
       </c>
       <c r="H75" t="str">
-        <v>earMUSIC</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>3:50</v>
       </c>
       <c r="H76" t="str">
-        <v>Y2K</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-09</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:43</v>
+        <v>3:24</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>MyKey</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-09</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>6:21</v>
+        <v>2:36</v>
       </c>
       <c r="H78" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Max McNown</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-09</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:46</v>
+        <v>3:34</v>
       </c>
       <c r="H79" t="str">
-        <v>Bryan Ferry</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-09</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:42</v>
+        <v>4:03</v>
       </c>
       <c r="H80" t="str">
-        <v>Saint Harison</v>
+        <v>ERNEST</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-09</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>3:31</v>
       </c>
       <c r="H81" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-09</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Catie Turner</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-09</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:22</v>
+        <v>5:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:53</v>
+        <v>3:47</v>
       </c>
       <c r="H84" t="str">
-        <v>Roxette</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:28</v>
+        <v>2:20</v>
       </c>
       <c r="H85" t="str">
-        <v>Marcin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-09</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:47</v>
+        <v>4:18</v>
       </c>
       <c r="H86" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-09</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:40</v>
+        <v>2:39</v>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>kenzie</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:49</v>
+        <v>3:52</v>
       </c>
       <c r="H88" t="str">
-        <v>Ava Max</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:49</v>
+        <v>4:01</v>
       </c>
       <c r="H89" t="str">
-        <v>U2</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:35</v>
+        <v>2:54</v>
       </c>
       <c r="H90" t="str">
-        <v>Taylor Swift</v>
+        <v>CHESCA</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:59</v>
+        <v>4:03</v>
       </c>
       <c r="H91" t="str">
-        <v>Kiana Ledé</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:38</v>
+        <v>4:50</v>
       </c>
       <c r="H92" t="str">
-        <v>Jessie Ware</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:46</v>
+        <v>3:06</v>
       </c>
       <c r="H93" t="str">
-        <v>Madison Beer</v>
+        <v>Y2K</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-09</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:08</v>
+        <v>2:43</v>
       </c>
       <c r="H94" t="str">
-        <v>Sean Stemaly</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:32</v>
+        <v>6:21</v>
       </c>
       <c r="H95" t="str">
-        <v>earMUSIC</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:39</v>
+        <v>2:46</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-09</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>2:42</v>
       </c>
       <c r="H97" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Self Esteem</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-09</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:27</v>
+        <v>2:59</v>
       </c>
       <c r="H99" t="str">
-        <v>070 Shake</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-09</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:49</v>
+        <v>2:22</v>
       </c>
       <c r="H100" t="str">
-        <v>georgemichael</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-09</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:52</v>
+        <v>3:53</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>Roxette</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-09</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:22</v>
+        <v>2:28</v>
       </c>
       <c r="H102" t="str">
-        <v>Foo Fighters</v>
+        <v>Marcin</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>American Girls</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>12 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:33</v>
+        <v>2:47</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>American Girls - Harry Styles</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ALGO TÚ</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>ALGO TÚ - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H104" t="str">
-        <v>Shakira</v>
+        <v>Laufey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>ALGO TÚ - Shakira</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>New Religion</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>New Religion - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H105" t="str">
-        <v>Bebe Rexha</v>
+        <v>Ava Max</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>New Religion - Bebe Rexha</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Where Do We Go</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Where Do We Go - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:56</v>
+        <v>4:49</v>
       </c>
       <c r="H106" t="str">
-        <v>Ayra Starr</v>
+        <v>U2</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Where Do We Go - Ayra Starr</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>if you wanna party, come over to my house</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Ö</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:51</v>
+        <v>3:35</v>
       </c>
       <c r="H107" t="str">
-        <v>Fcukers</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>if you wanna party, come over to my house - Fcukers</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>We Don’t Get Along</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>We Don’t Get Along - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H108" t="str">
-        <v>Juice WRLD</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>We Don’t Get Along - Juice WRLD</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Berghain (Remix)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Berghain (Remix) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:34</v>
+        <v>4:38</v>
       </c>
       <c r="H109" t="str">
-        <v>ROSALÍA</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/berghain-remix/1883156562</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Berghain (Remix) - ROSALÍA</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>bad bitch alert</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:24</v>
+        <v>3:46</v>
       </c>
       <c r="H110" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Medicine</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Medicine - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:34</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>Channel Tres</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>COME CLOSER</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>4:11</v>
+        <v>5:32</v>
       </c>
       <c r="H112" t="str">
-        <v>TOMORA</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dog</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Torn</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:37</v>
+        <v>4:39</v>
       </c>
       <c r="H113" t="str">
-        <v>Cobrah</v>
+        <v>georgemichael</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Dog - Cobrah</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Dance No More</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:14</v>
+        <v>3:40</v>
       </c>
       <c r="H114" t="str">
-        <v>Harry Styles</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Dance No More - Harry Styles</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Burial (from Mother Mary)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Burial (from Mother Mary) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:09</v>
+        <v>3:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Anne Hathaway</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Burial (from Mother Mary) - Anne Hathaway</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tweak</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tweak/1875414202</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Tweak - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>2:28</v>
+        <v>2:27</v>
       </c>
       <c r="H116" t="str">
-        <v>GIRLSET</v>
+        <v>070 Shake</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tweak/1875414200</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Tweak - GIRLSET</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ATTITUDE</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/attitude/1879665813</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ATTITUDE - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G117" t="str">
-        <v>3:05</v>
+        <v>4:49</v>
       </c>
       <c r="H117" t="str">
-        <v>aespa</v>
+        <v>georgemichael</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/attitude/1879665810</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>ATTITUDE - aespa</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Blame Texas</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Blame Texas - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G118" t="str">
-        <v>3:12</v>
+        <v>5:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Cody Johnson</v>
+        <v>georgemichael</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Blame Texas - Cody Johnson</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Kerosene</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Kerosene - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G119" t="str">
-        <v>3:26</v>
+        <v>3:22</v>
       </c>
       <c r="H119" t="str">
-        <v>The Warning</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v/>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
+        <v/>
       </c>
       <c r="L119" t="str">
-        <v>Kerosene - The Warning</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G120" t="str">
-        <v>3:28</v>
+        <v>4:08</v>
       </c>
       <c r="H120" t="str">
-        <v>J Balvin</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v/>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Save Me Tonight</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Save Me Tonight - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G121" t="str">
-        <v>3:16</v>
+        <v>3:44</v>
       </c>
       <c r="H121" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L121" t="str">
-        <v>Save Me Tonight - Jennifer Lopez</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Universal Soldier</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>HELP(2)</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:20</v>
+        <v>3:33</v>
       </c>
       <c r="H122" t="str">
-        <v>Depeche Mode</v>
+        <v>Shakira</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L122" t="str">
-        <v>Universal Soldier - Depeche Mode</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Coming Up Roses</v>
+        <v>New Religion</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:08</v>
+        <v>2:54</v>
       </c>
       <c r="H123" t="str">
-        <v>Harry Styles</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L123" t="str">
-        <v>Coming Up Roses - Harry Styles</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Light Over the Hill (from Reminders of Him)</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Single</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:43</v>
+        <v>2:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Noah Cyrus</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L124" t="str">
-        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Feel Better</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
+        <v>Ö</v>
       </c>
       <c r="G125" t="str">
-        <v>3:46</v>
+        <v>2:51</v>
       </c>
       <c r="H125" t="str">
-        <v>Koe Wetzel</v>
+        <v>Fcukers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L125" t="str">
-        <v>Feel Better - Koe Wetzel</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:02</v>
+        <v>2:29</v>
       </c>
       <c r="H126" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L126" t="str">
-        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Pinterest (Portuguese)</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Pinterest (Portuguese) - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G127" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H127" t="str">
-        <v>Anitta</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L127" t="str">
-        <v>Pinterest (Portuguese) - Anitta</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>San Charly</v>
+        <v>Medicine</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>San Charly - Single</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:54</v>
+        <v>2:34</v>
       </c>
       <c r="H128" t="str">
-        <v>Xavi</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L128" t="str">
-        <v>San Charly - Xavi</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Timelapse de Sol</v>
+        <v>Berghain (Remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
+        <v>https://music.apple.com/us/song/berghain-remix/1883156583</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>JuanesTeban</v>
+        <v>Berghain (Remix) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H129" t="str">
-        <v>Juanes</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
+        <v>https://music.apple.com/us/album/berghain-remix/1883156562</v>
       </c>
       <c r="L129" t="str">
-        <v>Timelapse de Sol - Juanes</v>
+        <v>Berghain (Remix) - ROSALÍA</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>solo (KETTAMA remix)</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>USB002 REMIXES</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G130" t="str">
-        <v>4:20</v>
+        <v>4:11</v>
       </c>
       <c r="H130" t="str">
-        <v>Fred again..</v>
+        <v>TOMORA</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L130" t="str">
-        <v>solo (KETTAMA remix) - Fred again..</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>It’s Been Too Long</v>
+        <v>American Girls</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Long Long Road</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G131" t="str">
-        <v>2:42</v>
+        <v>3:33</v>
       </c>
       <c r="H131" t="str">
-        <v>Ringo Starr</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L131" t="str">
-        <v>It’s Been Too Long - Ringo Starr</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Turn Your Heart Back On</v>
+        <v>Dog</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Atlanta</v>
+        <v>Torn</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Gnarls Barkley</v>
+        <v>Cobrah</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L132" t="str">
-        <v>Turn Your Heart Back On - Gnarls Barkley</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Devil You Know</v>
+        <v>Dance No More</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G133" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Maya Hawke</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L133" t="str">
-        <v>Devil You Know - Maya Hawke</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Earth, Wind &amp; California</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Jean</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:04</v>
+        <v>3:09</v>
       </c>
       <c r="H134" t="str">
-        <v>Yebba</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L134" t="str">
-        <v>Earth, Wind &amp; California - Yebba</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>400 Cities</v>
+        <v>Tweak</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Miracle Mile</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:17</v>
+        <v>2:28</v>
       </c>
       <c r="H135" t="str">
-        <v>Paul Russell</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L135" t="str">
-        <v>400 Cities - Paul Russell</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>THE BOXER</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>THE BOXER - Single</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:19</v>
+        <v>3:05</v>
       </c>
       <c r="H136" t="str">
-        <v>Kids That Fly</v>
+        <v>aespa</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L136" t="str">
-        <v>THE BOXER - Kids That Fly</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Borrowed Time</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Borrowed Time - Single</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:49</v>
+        <v>3:12</v>
       </c>
       <c r="H137" t="str">
-        <v>Sam Barber</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L137" t="str">
-        <v>Borrowed Time - Sam Barber</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>BREEZER</v>
+        <v>Kerosene</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/breezer/1858041251</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Lost on You</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>3:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Tigers Jaw</v>
+        <v>The Warning</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/breezer/1858041075</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L138" t="str">
-        <v>BREEZER - Tigers Jaw</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>War To Love</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Tragic Magic</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:46</v>
+        <v>3:28</v>
       </c>
       <c r="H139" t="str">
-        <v>Matt Corby</v>
+        <v>J Balvin</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L139" t="str">
-        <v>War To Love - Matt Corby</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Incompatibles</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Incompatibles - Single</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:53</v>
+        <v>3:16</v>
       </c>
       <c r="H140" t="str">
-        <v>Christian Nodal</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L140" t="str">
-        <v>Incompatibles - Christian Nodal</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Oídos Sordos</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Metamorfosis</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H141" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L141" t="str">
-        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Angel</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/angel/1877142613</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Angel - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G142" t="str">
-        <v>2:27</v>
+        <v>4:08</v>
       </c>
       <c r="H142" t="str">
-        <v>December 10</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/angel/1877142610</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L142" t="str">
-        <v>Angel - December 10</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trust Myself</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:03</v>
+        <v>4:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L143" t="str">
-        <v>Trust Myself - Katelyn Tarver</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Tears Ago</v>
+        <v>Feel Better</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Tears Ago - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:35</v>
+        <v>3:46</v>
       </c>
       <c r="H144" t="str">
-        <v>ili</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ili/1474855634</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L144" t="str">
-        <v>Tears Ago - ili</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bleed</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/bleed/1871562994</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>House of Cards</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G145" t="str">
-        <v>3:40</v>
+        <v>4:02</v>
       </c>
       <c r="H145" t="str">
-        <v>The Amity Affliction</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/bleed/1871562765</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L145" t="str">
-        <v>Bleed - The Amity Affliction</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Die for You</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Reflections</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:27</v>
+        <v>2:14</v>
       </c>
       <c r="H146" t="str">
-        <v>From Ashes to New</v>
+        <v>Anitta</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L146" t="str">
-        <v>Die for You - From Ashes to New</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
+        <v>San Charly</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:35</v>
+        <v>2:54</v>
       </c>
       <c r="H147" t="str">
-        <v>Honey Dijon</v>
+        <v>Xavi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L147" t="str">
-        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wish</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wish/1876893995</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Wish - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G148" t="str">
-        <v>2:45</v>
+        <v>3:05</v>
       </c>
       <c r="H148" t="str">
-        <v>Cash Cobain</v>
+        <v>Juanes</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wish/1876893993</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L148" t="str">
-        <v>Wish - Cash Cobain</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Clean Up Song</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Clean Up Song - EP</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G149" t="str">
-        <v>2:46</v>
+        <v>4:20</v>
       </c>
       <c r="H149" t="str">
-        <v>Tessa Violet</v>
+        <v>Fred again..</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L149" t="str">
-        <v>Clean Up Song - Tessa Violet</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Fantasy</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Fantasy - Single</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G150" t="str">
-        <v>3:42</v>
+        <v>2:42</v>
       </c>
       <c r="H150" t="str">
-        <v>Omarion</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/omarion/15559682</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L150" t="str">
-        <v>Fantasy - Omarion</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>why am i like this</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>why am i like this - Single</v>
+        <v>Atlanta</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>3:07</v>
       </c>
       <c r="H151" t="str">
-        <v>bbno$</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L151" t="str">
-        <v>why am i like this - bbno$</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>How the Fire Started</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>How the Fire Started - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G152" t="str">
-        <v>2:55</v>
+        <v>3:10</v>
       </c>
       <c r="H152" t="str">
-        <v>Eric Nam</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L152" t="str">
-        <v>How the Fire Started - Eric Nam</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Take Off Late</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mārara</v>
+        <v>Jean</v>
       </c>
       <c r="G153" t="str">
-        <v>3:23</v>
+        <v>3:04</v>
       </c>
       <c r="H153" t="str">
-        <v>15 15</v>
+        <v>Yebba</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L153" t="str">
-        <v>Take Off Late - 15 15</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>400 Cities</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>With No Due Respect</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G154" t="str">
-        <v>3:13</v>
+        <v>2:17</v>
       </c>
       <c r="H154" t="str">
-        <v>Foggieraw</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L154" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:06</v>
+        <v>3:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Denzel Curry</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L155" t="str">
-        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Wonderful Thing</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Wonderful Thing - Single</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H156" t="str">
-        <v>aron!</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L156" t="str">
-        <v>Wonderful Thing - aron!</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>leaving is easy</v>
+        <v>BREEZER</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>leaving is easy - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G157" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H157" t="str">
-        <v>almost monday</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L157" t="str">
-        <v>leaving is easy - almost monday</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>You and Me</v>
+        <v>War To Love</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>You and Me - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G158" t="str">
-        <v>2:46</v>
+        <v>3:46</v>
       </c>
       <c r="H158" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L158" t="str">
-        <v>You and Me - Cameron Whitcomb</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Tumbleweeds and Chewing Gum</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tumbleweeds and Chewing Gum - Single</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:39</v>
+        <v>2:53</v>
       </c>
       <c r="H159" t="str">
-        <v>Lily Meola</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L159" t="str">
-        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Everything to Nothing</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Everything to Nothing - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>3:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Michael Sanzone</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L160" t="str">
-        <v>Everything to Nothing - Michael Sanzone</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DELETED</v>
+        <v>Angel</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/deleted/1880220796</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>DELETED - Single</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:24</v>
+        <v>2:27</v>
       </c>
       <c r="H161" t="str">
-        <v>vaultboy</v>
+        <v>December 10</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/deleted/1880220075</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L161" t="str">
-        <v>DELETED - vaultboy</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A Thousand Years</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Thousand Years - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G162" t="str">
-        <v>3:00</v>
+        <v>3:03</v>
       </c>
       <c r="H162" t="str">
-        <v>John Michael Howell</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L162" t="str">
-        <v>A Thousand Years - John Michael Howell</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Freedom (feat. EZI)</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Freedom (feat. EZI) - Single</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>5:29</v>
+        <v>2:35</v>
       </c>
       <c r="H163" t="str">
-        <v>Kaskade</v>
+        <v>ili</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L163" t="str">
-        <v>Freedom (feat. EZI) - Kaskade</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
+        <v>Bleed</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>House of Cards</v>
       </c>
       <c r="G164" t="str">
-        <v>3:16</v>
+        <v>3:40</v>
       </c>
       <c r="H164" t="str">
-        <v>MORGXN</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L164" t="str">
-        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>To Myself</v>
+        <v>Die for You</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>MINDFIELDS</v>
+        <v>Reflections</v>
       </c>
       <c r="G165" t="str">
-        <v>3:40</v>
+        <v>3:27</v>
       </c>
       <c r="H165" t="str">
-        <v>Alicia Creti</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L165" t="str">
-        <v>To Myself - Alicia Creti</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>TABOO</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/taboo/1880750236</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>TABOO - Single</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:45</v>
+        <v>3:35</v>
       </c>
       <c r="H166" t="str">
-        <v>Isaiah Falls</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/taboo/1880750235</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L166" t="str">
-        <v>TABOO - Isaiah Falls</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Under The Table (feat. Chris Lane)</v>
+        <v>Wish</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Under The Table (feat. Chris Lane) - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:52</v>
+        <v>2:45</v>
       </c>
       <c r="H167" t="str">
-        <v>Two Friends</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L167" t="str">
-        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Be Mine</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Be Mine - Single</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>1:53</v>
+        <v>2:46</v>
       </c>
       <c r="H168" t="str">
-        <v>James Hype</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L168" t="str">
-        <v>Be Mine - James Hype</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
+        <v>Fantasy</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:11</v>
+        <v>3:42</v>
       </c>
       <c r="H169" t="str">
-        <v>ANOTR</v>
+        <v>Omarion</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L169" t="str">
-        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Evil Against Me</v>
+        <v>why am i like this</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Evil Against Me - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:24</v>
+        <v>2:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Shaya Zamora</v>
+        <v>bbno$</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L170" t="str">
-        <v>Evil Against Me - Shaya Zamora</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Still Do</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/still-do/1877250216</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Still Do - Single</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:03</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Anne Wilson</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/still-do/1877250210</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L171" t="str">
-        <v>Still Do - Anne Wilson</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>DIE 4 ME</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>DIE 4 ME - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G172" t="str">
-        <v>2:37</v>
+        <v>3:23</v>
       </c>
       <c r="H172" t="str">
-        <v>Taylor Hill</v>
+        <v>15 15</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L172" t="str">
-        <v>DIE 4 ME - Taylor Hill</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Havin'</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/havin/1878165152</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Havin' - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G173" t="str">
-        <v>2:49</v>
+        <v>3:13</v>
       </c>
       <c r="H173" t="str">
-        <v>1K Phew</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/havin/18781651